--- a/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C338B980-6F2D-4BA9-9AC7-1251737CCD82}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5AC1432C-0454-491C-B311-8CBC9194BD16}"/>
   </bookViews>
@@ -68,12 +68,6 @@
     <t>GILD</t>
   </si>
   <si>
-    <t>171.22B</t>
-  </si>
-  <si>
-    <t>+115.05</t>
-  </si>
-  <si>
     <t>3.84</t>
   </si>
   <si>
@@ -86,27 +80,9 @@
     <t>Resilient</t>
   </si>
   <si>
-    <t>Grifols, S.A.</t>
-  </si>
-  <si>
-    <t>GRF.MC</t>
-  </si>
-  <si>
-    <t>7.81B</t>
-  </si>
-  <si>
-    <t>+89.12</t>
-  </si>
-  <si>
-    <t>1.14</t>
-  </si>
-  <si>
     <t>6.0</t>
   </si>
   <si>
-    <t>-2.67</t>
-  </si>
-  <si>
     <t>Robust</t>
   </si>
   <si>
@@ -116,12 +92,6 @@
     <t>AMN</t>
   </si>
   <si>
-    <t>777.74M</t>
-  </si>
-  <si>
-    <t>+44.13</t>
-  </si>
-  <si>
     <t>2.40</t>
   </si>
   <si>
@@ -137,12 +107,6 @@
     <t>CTKB</t>
   </si>
   <si>
-    <t>588.91M</t>
-  </si>
-  <si>
-    <t>+33.84</t>
-  </si>
-  <si>
     <t>3.89</t>
   </si>
   <si>
@@ -152,21 +116,6 @@
     <t>-23864.25</t>
   </si>
   <si>
-    <t>Chemed Corporation</t>
-  </si>
-  <si>
-    <t>CHE</t>
-  </si>
-  <si>
-    <t>5.54B</t>
-  </si>
-  <si>
-    <t>+29.19</t>
-  </si>
-  <si>
-    <t>10.35</t>
-  </si>
-  <si>
     <t>-2.83</t>
   </si>
   <si>
@@ -176,12 +125,6 @@
     <t>COLL</t>
   </si>
   <si>
-    <t>1.09B</t>
-  </si>
-  <si>
-    <t>+12.06</t>
-  </si>
-  <si>
     <t>1.58</t>
   </si>
   <si>
@@ -191,33 +134,12 @@
     <t>-2.90</t>
   </si>
   <si>
-    <t>Cross Country Healthcare, Inc.</t>
-  </si>
-  <si>
-    <t>CCRN</t>
-  </si>
-  <si>
-    <t>319.55M</t>
-  </si>
-  <si>
-    <t>+7.20</t>
-  </si>
-  <si>
-    <t>1.59</t>
-  </si>
-  <si>
-    <t>-5.13</t>
-  </si>
-  <si>
     <t>Pro-Dex, Inc.</t>
   </si>
   <si>
     <t>PDEX</t>
   </si>
   <si>
-    <t>173.51M</t>
-  </si>
-  <si>
     <t>-3.39</t>
   </si>
   <si>
@@ -233,66 +155,21 @@
     <t>SNWV</t>
   </si>
   <si>
-    <t>176.49M</t>
-  </si>
-  <si>
-    <t>-1.94</t>
-  </si>
-  <si>
     <t>-2.97</t>
   </si>
   <si>
     <t>-3.53</t>
   </si>
   <si>
-    <t>Laboratorios Farmaceuticos Rovi, S.A.</t>
-  </si>
-  <si>
-    <t>ROVI.MC</t>
-  </si>
-  <si>
-    <t>5.12B</t>
-  </si>
-  <si>
-    <t>-15.28</t>
-  </si>
-  <si>
-    <t>9.75</t>
-  </si>
-  <si>
     <t>-2.71</t>
   </si>
   <si>
-    <t>Sysmex Corporation</t>
-  </si>
-  <si>
-    <t>6869.T</t>
-  </si>
-  <si>
-    <t>5.64B</t>
-  </si>
-  <si>
-    <t>+87.69</t>
-  </si>
-  <si>
-    <t>5.36</t>
-  </si>
-  <si>
-    <t>-2.42</t>
-  </si>
-  <si>
     <t>Fresenius Medical Care AG &amp; Co. KGaA</t>
   </si>
   <si>
     <t>FME.DE</t>
   </si>
   <si>
-    <t>13.55B</t>
-  </si>
-  <si>
-    <t>+69.09</t>
-  </si>
-  <si>
     <t>1.31</t>
   </si>
   <si>
@@ -308,12 +185,6 @@
     <t>MASI</t>
   </si>
   <si>
-    <t>9.56B</t>
-  </si>
-  <si>
-    <t>+55.85</t>
-  </si>
-  <si>
     <t>7.41</t>
   </si>
   <si>
@@ -326,12 +197,6 @@
     <t>SN.L</t>
   </si>
   <si>
-    <t>14.85B</t>
-  </si>
-  <si>
-    <t>+38.66</t>
-  </si>
-  <si>
     <t>5.23</t>
   </si>
   <si>
@@ -344,12 +209,6 @@
     <t>HALO</t>
   </si>
   <si>
-    <t>8.30B</t>
-  </si>
-  <si>
-    <t>+55.27</t>
-  </si>
-  <si>
     <t>3.91</t>
   </si>
   <si>
@@ -359,12 +218,6 @@
     <t>4568.T</t>
   </si>
   <si>
-    <t>34.28B</t>
-  </si>
-  <si>
-    <t>+99.29</t>
-  </si>
-  <si>
     <t>3.63</t>
   </si>
   <si>
@@ -377,12 +230,6 @@
     <t>UHS</t>
   </si>
   <si>
-    <t>11.60B</t>
-  </si>
-  <si>
-    <t>+48.13</t>
-  </si>
-  <si>
     <t>3.19</t>
   </si>
   <si>
@@ -392,12 +239,6 @@
     <t>4503.T</t>
   </si>
   <si>
-    <t>28.82B</t>
-  </si>
-  <si>
-    <t>+32.77</t>
-  </si>
-  <si>
     <t>2.29</t>
   </si>
   <si>
@@ -410,12 +251,6 @@
     <t>EXEL</t>
   </si>
   <si>
-    <t>12.19B</t>
-  </si>
-  <si>
-    <t>+26.38</t>
-  </si>
-  <si>
     <t>12.62</t>
   </si>
   <si>
@@ -428,75 +263,12 @@
     <t>7733.T</t>
   </si>
   <si>
-    <t>10.99B</t>
-  </si>
-  <si>
-    <t>+10.69</t>
-  </si>
-  <si>
-    <t>3.29</t>
-  </si>
-  <si>
-    <t>-2.76</t>
-  </si>
-  <si>
-    <t>Definitive Healthcare Corp.</t>
-  </si>
-  <si>
-    <t>DH</t>
-  </si>
-  <si>
-    <t>109.85M</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>0.00</t>
-  </si>
-  <si>
-    <t>-2.18</t>
-  </si>
-  <si>
-    <t>Esperion Therapeutics, Inc.</t>
-  </si>
-  <si>
-    <t>ESPR</t>
-  </si>
-  <si>
-    <t>424.04M</t>
-  </si>
-  <si>
-    <t>+181.86</t>
-  </si>
-  <si>
-    <t>Simulations Plus, Inc.</t>
-  </si>
-  <si>
-    <t>SLP</t>
-  </si>
-  <si>
-    <t>289.56M</t>
-  </si>
-  <si>
-    <t>+116.77</t>
-  </si>
-  <si>
-    <t>10.74</t>
-  </si>
-  <si>
     <t>BioMarin Pharmaceutical Inc.</t>
   </si>
   <si>
     <t>BMRN</t>
   </si>
   <si>
-    <t>10.48B</t>
-  </si>
-  <si>
-    <t>+85.45</t>
-  </si>
-  <si>
     <t>5.73</t>
   </si>
   <si>
@@ -509,141 +281,45 @@
     <t>SUNPHARMA.NS</t>
   </si>
   <si>
-    <t>43.40B</t>
-  </si>
-  <si>
-    <t>+49.02</t>
-  </si>
-  <si>
     <t>15.35</t>
   </si>
   <si>
     <t>-3.54</t>
   </si>
   <si>
-    <t>Progyny, Inc.</t>
-  </si>
-  <si>
-    <t>PGNY</t>
-  </si>
-  <si>
-    <t>1.54B</t>
-  </si>
-  <si>
-    <t>+75.77</t>
-  </si>
-  <si>
-    <t>8.48</t>
-  </si>
-  <si>
-    <t>-2.87</t>
-  </si>
-  <si>
     <t>Innoviva, Inc.</t>
   </si>
   <si>
     <t>INVA</t>
   </si>
   <si>
-    <t>1.63B</t>
-  </si>
-  <si>
-    <t>+57.38</t>
-  </si>
-  <si>
     <t>3.06</t>
   </si>
   <si>
     <t>-1.63</t>
   </si>
   <si>
-    <t>Ardent Health Partners, LLC</t>
-  </si>
-  <si>
-    <t>ARDT</t>
-  </si>
-  <si>
-    <t>1.39B</t>
-  </si>
-  <si>
-    <t>+65.59</t>
-  </si>
-  <si>
-    <t>1.94</t>
-  </si>
-  <si>
     <t>4.0</t>
   </si>
   <si>
-    <t>0.92</t>
-  </si>
-  <si>
     <t>Globus Medical, Inc.</t>
   </si>
   <si>
     <t>GMED</t>
   </si>
   <si>
-    <t>12.87B</t>
-  </si>
-  <si>
-    <t>+47.07</t>
-  </si>
-  <si>
     <t>11.29</t>
   </si>
   <si>
-    <t>Cigna Corporation</t>
-  </si>
-  <si>
-    <t>CI</t>
-  </si>
-  <si>
-    <t>74.10B</t>
-  </si>
-  <si>
-    <t>+44.94</t>
-  </si>
-  <si>
-    <t>2.67</t>
-  </si>
-  <si>
-    <t>-2.68</t>
-  </si>
-  <si>
-    <t>Agios Pharmaceuticals, Inc.</t>
-  </si>
-  <si>
-    <t>AGIO</t>
-  </si>
-  <si>
-    <t>2.04B</t>
-  </si>
-  <si>
-    <t>+24.87</t>
-  </si>
-  <si>
-    <t>8.12</t>
-  </si>
-  <si>
     <t>2.0</t>
   </si>
   <si>
-    <t>-1.71</t>
-  </si>
-  <si>
     <t>Haleon plc</t>
   </si>
   <si>
     <t>HLN.L</t>
   </si>
   <si>
-    <t>43.42B</t>
-  </si>
-  <si>
-    <t>+24.16</t>
-  </si>
-  <si>
     <t>3.04</t>
   </si>
   <si>
@@ -656,12 +332,6 @@
     <t>ANAB</t>
   </si>
   <si>
-    <t>1.88B</t>
-  </si>
-  <si>
-    <t>+133.94</t>
-  </si>
-  <si>
     <t>1.61</t>
   </si>
   <si>
@@ -674,255 +344,48 @@
     <t>4007.SR</t>
   </si>
   <si>
-    <t>1.15B</t>
-  </si>
-  <si>
-    <t>+29.21</t>
-  </si>
-  <si>
     <t>5.07</t>
   </si>
   <si>
     <t>-3.26</t>
   </si>
   <si>
-    <t>U.S. Physical Therapy, Inc.</t>
-  </si>
-  <si>
-    <t>USPH</t>
-  </si>
-  <si>
-    <t>1.16B</t>
-  </si>
-  <si>
-    <t>+64.14</t>
-  </si>
-  <si>
-    <t>2.68</t>
-  </si>
-  <si>
-    <t>Claritev Corporation</t>
-  </si>
-  <si>
-    <t>CTEV</t>
-  </si>
-  <si>
-    <t>338.39M</t>
-  </si>
-  <si>
-    <t>+43.52</t>
-  </si>
-  <si>
-    <t>-0.40</t>
-  </si>
-  <si>
-    <t>Delcath Systems, Inc.</t>
-  </si>
-  <si>
-    <t>DCTH</t>
-  </si>
-  <si>
-    <t>389.02M</t>
-  </si>
-  <si>
-    <t>-4.97</t>
-  </si>
-  <si>
-    <t>12.57</t>
-  </si>
-  <si>
-    <t>-5.84</t>
-  </si>
-  <si>
-    <t>AirSculpt Technologies, Inc.</t>
-  </si>
-  <si>
-    <t>AIRS</t>
-  </si>
-  <si>
-    <t>154.75M</t>
-  </si>
-  <si>
-    <t>+39.06</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>-4.46</t>
-  </si>
-  <si>
-    <t>Gossamer Bio, Inc.</t>
-  </si>
-  <si>
-    <t>GOSS</t>
-  </si>
-  <si>
-    <t>101.92M</t>
-  </si>
-  <si>
-    <t>+108.52</t>
-  </si>
-  <si>
-    <t>-12.52</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>-3.34</t>
-  </si>
-  <si>
-    <t>The Joint Corp.</t>
-  </si>
-  <si>
-    <t>JYNT</t>
-  </si>
-  <si>
-    <t>139.54M</t>
-  </si>
-  <si>
-    <t>+27.87</t>
-  </si>
-  <si>
-    <t>2.39</t>
-  </si>
-  <si>
-    <t>-2.69</t>
-  </si>
-  <si>
-    <t>SI-BONE, Inc.</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>613.02M</t>
-  </si>
-  <si>
-    <t>+21.22</t>
-  </si>
-  <si>
-    <t>7.29</t>
-  </si>
-  <si>
-    <t>-2.84</t>
-  </si>
-  <si>
-    <t>Penumbra, Inc.</t>
-  </si>
-  <si>
-    <t>PEN</t>
-  </si>
-  <si>
-    <t>12.93B</t>
-  </si>
-  <si>
-    <t>+45.72</t>
-  </si>
-  <si>
-    <t>20.17</t>
-  </si>
-  <si>
-    <t>-3.32</t>
-  </si>
-  <si>
-    <t>Steady</t>
-  </si>
-  <si>
     <t>Align Technology, Inc.</t>
   </si>
   <si>
     <t>ALGN</t>
   </si>
   <si>
-    <t>13.79B</t>
-  </si>
-  <si>
-    <t>+9.90</t>
-  </si>
-  <si>
     <t>4.77</t>
   </si>
   <si>
     <t>-2.52</t>
   </si>
   <si>
-    <t>West Pharmaceutical Services, Inc.</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>19.79B</t>
-  </si>
-  <si>
-    <t>+1.95</t>
-  </si>
-  <si>
-    <t>13.91</t>
-  </si>
-  <si>
     <t>Edwards Lifesciences Corporation</t>
   </si>
   <si>
     <t>EW</t>
   </si>
   <si>
-    <t>47.36B</t>
-  </si>
-  <si>
     <t>-2.28</t>
   </si>
   <si>
     <t>11.63</t>
   </si>
   <si>
-    <t>-2.72</t>
-  </si>
-  <si>
     <t>Zoetis Inc.</t>
   </si>
   <si>
     <t>ZTS</t>
   </si>
   <si>
-    <t>54.27B</t>
-  </si>
-  <si>
-    <t>+35.64</t>
-  </si>
-  <si>
-    <t>Terumo Corporation</t>
-  </si>
-  <si>
-    <t>4543.T</t>
-  </si>
-  <si>
-    <t>20.22B</t>
-  </si>
-  <si>
-    <t>+29.00</t>
-  </si>
-  <si>
-    <t>4.28</t>
-  </si>
-  <si>
-    <t>-2.32</t>
-  </si>
-  <si>
     <t>Sonova Holding AG</t>
   </si>
   <si>
     <t>SOON.SW</t>
   </si>
   <si>
-    <t>14.59B</t>
-  </si>
-  <si>
-    <t>+19.98</t>
-  </si>
-  <si>
     <t>4.58</t>
   </si>
   <si>
@@ -944,22 +407,559 @@
     <t>4.18</t>
   </si>
   <si>
-    <t>Ambu A/S</t>
-  </si>
-  <si>
-    <t>AMBU-B.CO</t>
-  </si>
-  <si>
-    <t>2.98B</t>
-  </si>
-  <si>
-    <t>+103.06</t>
-  </si>
-  <si>
-    <t>11.48</t>
-  </si>
-  <si>
-    <t>-2.60</t>
+    <t>WuXi Biologics (Cayman) Inc.</t>
+  </si>
+  <si>
+    <t>2269.HK</t>
+  </si>
+  <si>
+    <t>17.22B</t>
+  </si>
+  <si>
+    <t>+82.19</t>
+  </si>
+  <si>
+    <t>8.13</t>
+  </si>
+  <si>
+    <t>Nahdi Medical Company</t>
+  </si>
+  <si>
+    <t>4164.SR</t>
+  </si>
+  <si>
+    <t>3.60B</t>
+  </si>
+  <si>
+    <t>+73.87</t>
+  </si>
+  <si>
+    <t>4.64</t>
+  </si>
+  <si>
+    <t>-3.43</t>
+  </si>
+  <si>
+    <t>13.25B</t>
+  </si>
+  <si>
+    <t>+72.27</t>
+  </si>
+  <si>
+    <t>Mouwasat Medical Services Company</t>
+  </si>
+  <si>
+    <t>4002.SR</t>
+  </si>
+  <si>
+    <t>3.69B</t>
+  </si>
+  <si>
+    <t>+65.20</t>
+  </si>
+  <si>
+    <t>6.36</t>
+  </si>
+  <si>
+    <t>-3.24</t>
+  </si>
+  <si>
+    <t>9.57B</t>
+  </si>
+  <si>
+    <t>+55.64</t>
+  </si>
+  <si>
+    <t>13.57B</t>
+  </si>
+  <si>
+    <t>+51.83</t>
+  </si>
+  <si>
+    <t>7.83B</t>
+  </si>
+  <si>
+    <t>+64.61</t>
+  </si>
+  <si>
+    <t>783.90M</t>
+  </si>
+  <si>
+    <t>+43.00</t>
+  </si>
+  <si>
+    <t>562.08M</t>
+  </si>
+  <si>
+    <t>+40.23</t>
+  </si>
+  <si>
+    <t>1.03B</t>
+  </si>
+  <si>
+    <t>+18.65</t>
+  </si>
+  <si>
+    <t>Lonza Group AG</t>
+  </si>
+  <si>
+    <t>LONN.SW</t>
+  </si>
+  <si>
+    <t>42.90B</t>
+  </si>
+  <si>
+    <t>+18.13</t>
+  </si>
+  <si>
+    <t>3.88</t>
+  </si>
+  <si>
+    <t>-2.56</t>
+  </si>
+  <si>
+    <t>10.56B</t>
+  </si>
+  <si>
+    <t>+33.94</t>
+  </si>
+  <si>
+    <t>3.66</t>
+  </si>
+  <si>
+    <t>-2.51</t>
+  </si>
+  <si>
+    <t>29.02B</t>
+  </si>
+  <si>
+    <t>+134.38</t>
+  </si>
+  <si>
+    <t>11.09B</t>
+  </si>
+  <si>
+    <t>+54.98</t>
+  </si>
+  <si>
+    <t>27.74B</t>
+  </si>
+  <si>
+    <t>+37.37</t>
+  </si>
+  <si>
+    <t>41.24B</t>
+  </si>
+  <si>
+    <t>+54.09</t>
+  </si>
+  <si>
+    <t>12.20B</t>
+  </si>
+  <si>
+    <t>+26.23</t>
+  </si>
+  <si>
+    <t>43.05B</t>
+  </si>
+  <si>
+    <t>+25.35</t>
+  </si>
+  <si>
+    <t>WuXi AppTec Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2359.HK</t>
+  </si>
+  <si>
+    <t>45.10B</t>
+  </si>
+  <si>
+    <t>+24.65</t>
+  </si>
+  <si>
+    <t>8.21</t>
+  </si>
+  <si>
+    <t>-3.37</t>
+  </si>
+  <si>
+    <t>IDEXX Laboratories, Inc.</t>
+  </si>
+  <si>
+    <t>IDXX</t>
+  </si>
+  <si>
+    <t>45.33B</t>
+  </si>
+  <si>
+    <t>+14.33</t>
+  </si>
+  <si>
+    <t>23.99</t>
+  </si>
+  <si>
+    <t>13.75B</t>
+  </si>
+  <si>
+    <t>+10.17</t>
+  </si>
+  <si>
+    <t>160.14M</t>
+  </si>
+  <si>
+    <t>+8.07</t>
+  </si>
+  <si>
+    <t>48.74B</t>
+  </si>
+  <si>
+    <t>+7.88</t>
+  </si>
+  <si>
+    <t>-3.52</t>
+  </si>
+  <si>
+    <t>51.83B</t>
+  </si>
+  <si>
+    <t>+42.04</t>
+  </si>
+  <si>
+    <t>Abbott Laboratories</t>
+  </si>
+  <si>
+    <t>ABT</t>
+  </si>
+  <si>
+    <t>159.20B</t>
+  </si>
+  <si>
+    <t>+27.64</t>
+  </si>
+  <si>
+    <t>5.62</t>
+  </si>
+  <si>
+    <t>-3.62</t>
+  </si>
+  <si>
+    <t>Ginkgo Bioworks Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>DNA</t>
+  </si>
+  <si>
+    <t>436.45M</t>
+  </si>
+  <si>
+    <t>+7.12</t>
+  </si>
+  <si>
+    <t>-7.61</t>
+  </si>
+  <si>
+    <t>169.29M</t>
+  </si>
+  <si>
+    <t>-0.98</t>
+  </si>
+  <si>
+    <t>Healthcare Services Group, Inc.</t>
+  </si>
+  <si>
+    <t>HCSG</t>
+  </si>
+  <si>
+    <t>1.57B</t>
+  </si>
+  <si>
+    <t>-14.41</t>
+  </si>
+  <si>
+    <t>6.94</t>
+  </si>
+  <si>
+    <t>1.59B</t>
+  </si>
+  <si>
+    <t>+61.86</t>
+  </si>
+  <si>
+    <t>HOYA Corporation</t>
+  </si>
+  <si>
+    <t>7741.T</t>
+  </si>
+  <si>
+    <t>60.73B</t>
+  </si>
+  <si>
+    <t>-7.43</t>
+  </si>
+  <si>
+    <t>21.73</t>
+  </si>
+  <si>
+    <t>-2.30</t>
+  </si>
+  <si>
+    <t>Harmony Biosciences Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>HRMY</t>
+  </si>
+  <si>
+    <t>1.77B</t>
+  </si>
+  <si>
+    <t>+50.84</t>
+  </si>
+  <si>
+    <t>13.30B</t>
+  </si>
+  <si>
+    <t>+31.14</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
+  </si>
+  <si>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>20.54B</t>
+  </si>
+  <si>
+    <t>+52.63</t>
+  </si>
+  <si>
+    <t>2.77</t>
+  </si>
+  <si>
+    <t>-2.81</t>
+  </si>
+  <si>
+    <t>1.64B</t>
+  </si>
+  <si>
+    <t>+168.22</t>
+  </si>
+  <si>
+    <t>162.22B</t>
+  </si>
+  <si>
+    <t>+126.99</t>
+  </si>
+  <si>
+    <t>Sanofi</t>
+  </si>
+  <si>
+    <t>SAN.PA</t>
+  </si>
+  <si>
+    <t>113.01B</t>
+  </si>
+  <si>
+    <t>+64.89</t>
+  </si>
+  <si>
+    <t>1.84</t>
+  </si>
+  <si>
+    <t>-2.58</t>
+  </si>
+  <si>
+    <t>10.20B</t>
+  </si>
+  <si>
+    <t>+90.54</t>
+  </si>
+  <si>
+    <t>Neurocrine Biosciences, Inc.</t>
+  </si>
+  <si>
+    <t>NBIX</t>
+  </si>
+  <si>
+    <t>12.70B</t>
+  </si>
+  <si>
+    <t>+57.39</t>
+  </si>
+  <si>
+    <t>7.80</t>
+  </si>
+  <si>
+    <t>Madrigal Pharmaceuticals, Inc.</t>
+  </si>
+  <si>
+    <t>MDGL</t>
+  </si>
+  <si>
+    <t>11.50B</t>
+  </si>
+  <si>
+    <t>+56.11</t>
+  </si>
+  <si>
+    <t>21.16</t>
+  </si>
+  <si>
+    <t>-1.85</t>
+  </si>
+  <si>
+    <t>Pro Medicus Limited</t>
+  </si>
+  <si>
+    <t>PME.AX</t>
+  </si>
+  <si>
+    <t>10.33B</t>
+  </si>
+  <si>
+    <t>+55.28</t>
+  </si>
+  <si>
+    <t>98.62</t>
+  </si>
+  <si>
+    <t>-0.59</t>
+  </si>
+  <si>
+    <t>12.82B</t>
+  </si>
+  <si>
+    <t>+47.65</t>
+  </si>
+  <si>
+    <t>Medpace Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>11.68B</t>
+  </si>
+  <si>
+    <t>+32.37</t>
+  </si>
+  <si>
+    <t>7.14</t>
+  </si>
+  <si>
+    <t>1.10B</t>
+  </si>
+  <si>
+    <t>+35.31</t>
+  </si>
+  <si>
+    <t>LifeStance Health Group, Inc.</t>
+  </si>
+  <si>
+    <t>LFST</t>
+  </si>
+  <si>
+    <t>2.72B</t>
+  </si>
+  <si>
+    <t>+71.06</t>
+  </si>
+  <si>
+    <t>2.65</t>
+  </si>
+  <si>
+    <t>-3.15</t>
+  </si>
+  <si>
+    <t>Dallah Healthcare Company</t>
+  </si>
+  <si>
+    <t>4004.SR</t>
+  </si>
+  <si>
+    <t>3.30B</t>
+  </si>
+  <si>
+    <t>+61.95</t>
+  </si>
+  <si>
+    <t>3.93</t>
+  </si>
+  <si>
+    <t>-3.38</t>
+  </si>
+  <si>
+    <t>Bavarian Nordic A/S</t>
+  </si>
+  <si>
+    <t>BAVA.CO</t>
+  </si>
+  <si>
+    <t>2.28B</t>
+  </si>
+  <si>
+    <t>+45.67</t>
+  </si>
+  <si>
+    <t>6.46</t>
+  </si>
+  <si>
+    <t>-3.01</t>
+  </si>
+  <si>
+    <t>Tenet Healthcare Corporation</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>16.42B</t>
+  </si>
+  <si>
+    <t>+39.33</t>
+  </si>
+  <si>
+    <t>1.98</t>
+  </si>
+  <si>
+    <t>-2.47</t>
+  </si>
+  <si>
+    <t>Prestige Consumer Healthcare Inc.</t>
+  </si>
+  <si>
+    <t>PBH</t>
+  </si>
+  <si>
+    <t>2.82B</t>
+  </si>
+  <si>
+    <t>+35.63</t>
+  </si>
+  <si>
+    <t>2.46</t>
+  </si>
+  <si>
+    <t>-2.22</t>
+  </si>
+  <si>
+    <t>Option Care Health, Inc.</t>
+  </si>
+  <si>
+    <t>OPCH</t>
+  </si>
+  <si>
+    <t>4.49B</t>
+  </si>
+  <si>
+    <t>+34.15</t>
+  </si>
+  <si>
+    <t>3.53</t>
+  </si>
+  <si>
+    <t>-2.46</t>
   </si>
 </sst>
 </file>
@@ -1334,39 +1334,39 @@
   <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="51" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="51" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1375,28 +1375,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>9</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1412,36 +1412,36 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="F4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="J4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1449,36 +1449,36 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="J6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1486,36 +1486,36 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="J8" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1523,36 +1523,36 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1560,36 +1560,36 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1597,36 +1597,36 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>147</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I14" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1634,36 +1634,36 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1671,36 +1671,36 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="G18" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I18" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="J18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1708,36 +1708,36 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="H20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I20" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="J20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1745,36 +1745,36 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="H22" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I22" t="s">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="J22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1782,36 +1782,36 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>161</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="H24" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="I24" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="J24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1819,36 +1819,36 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I26" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="J26" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1856,36 +1856,36 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="H28" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="J28" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1893,36 +1893,36 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="E30" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="I30" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="J30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1930,36 +1930,36 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>170</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="F32" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="I32" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="J32" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1967,36 +1967,36 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="F34" t="s">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="G34" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I34" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="J34" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2004,36 +2004,36 @@
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="G36" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="I36" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="J36" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2041,36 +2041,36 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="F38" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="G38" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="H38" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I38" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J38" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2078,36 +2078,36 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="E40" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="F40" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="G40" t="s">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="H40" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I40" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="J40" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2115,36 +2115,36 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="E42" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="F42" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="G42" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I42" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="J42" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2152,28 +2152,28 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="D44" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="E44" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="F44" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="G44" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I44" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="J44" t="s">
         <v>15</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>141</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2189,28 +2189,28 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>191</v>
       </c>
       <c r="E46" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="F46" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="G46" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="H46" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I46" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="J46" t="s">
         <v>15</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2226,28 +2226,28 @@
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="E48" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="F48" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="G48" t="s">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I48" t="s">
-        <v>154</v>
+        <v>36</v>
       </c>
       <c r="J48" t="s">
         <v>15</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2263,28 +2263,28 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="C50" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="D50" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="E50" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="F50" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="G50" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="H50" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="J50" t="s">
         <v>15</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -2300,28 +2300,28 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="D52" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="E52" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="F52" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="G52" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="H52" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s">
-        <v>166</v>
+        <v>12</v>
       </c>
       <c r="J52" t="s">
         <v>15</v>
@@ -2329,7 +2329,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -2337,36 +2337,36 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="E54" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="G54" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="H54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I54" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="J54" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>168</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -2374,36 +2374,36 @@
         <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="C56" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="D56" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="E56" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="F56" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="G56" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="H56" t="s">
-        <v>178</v>
+        <v>30</v>
       </c>
       <c r="I56" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="J56" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -2411,28 +2411,28 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="C58" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="D58" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="E58" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="F58" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="G58" t="s">
-        <v>184</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" t="s">
         <v>86</v>
-      </c>
-      <c r="I58" t="s">
-        <v>74</v>
       </c>
       <c r="J58" t="s">
         <v>15</v>
@@ -2440,7 +2440,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -2448,36 +2448,36 @@
         <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="C60" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="D60" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="E60" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="F60" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="G60" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="H60" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="I60" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="J60" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -2485,36 +2485,36 @@
         <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="C62" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="D62" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="E62" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="F62" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="G62" t="s">
-        <v>195</v>
+        <v>53</v>
       </c>
       <c r="H62" t="s">
-        <v>196</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s">
-        <v>197</v>
+        <v>117</v>
       </c>
       <c r="J62" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -2522,36 +2522,36 @@
         <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>198</v>
+        <v>114</v>
       </c>
       <c r="C64" t="s">
-        <v>198</v>
+        <v>114</v>
       </c>
       <c r="D64" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E64" t="s">
-        <v>198</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="G64" t="s">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="H64" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="I64" t="s">
-        <v>203</v>
+        <v>117</v>
       </c>
       <c r="J64" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>199</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -2559,28 +2559,28 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="C66" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="D66" t="s">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="E66" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="F66" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="G66" t="s">
-        <v>208</v>
+        <v>122</v>
       </c>
       <c r="H66" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I66" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
       <c r="J66" t="s">
         <v>15</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>205</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2596,28 +2596,28 @@
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="C68" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D68" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="E68" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="F68" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="G68" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="H68" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I68" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="J68" t="s">
         <v>15</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -2633,36 +2633,36 @@
         <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>216</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
-        <v>216</v>
+        <v>96</v>
       </c>
       <c r="D70" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E70" t="s">
-        <v>216</v>
+        <v>96</v>
       </c>
       <c r="F70" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G70" t="s">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="H70" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I70" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="J70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>217</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -2670,36 +2670,36 @@
         <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>221</v>
+        <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>221</v>
+        <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E72" t="s">
-        <v>221</v>
+        <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="G72" t="s">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="H72" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I72" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="J72" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>222</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -2707,28 +2707,28 @@
         <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C74" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="D74" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E74" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="F74" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="G74" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="H74" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I74" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="J74" t="s">
         <v>15</v>
@@ -2736,7 +2736,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -2744,36 +2744,36 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="C76" t="s">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="D76" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E76" t="s">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G76" t="s">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="H76" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I76" t="s">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="J76" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>233</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -2781,36 +2781,36 @@
         <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C78" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D78" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E78" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F78" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="G78" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="H78" t="s">
-        <v>243</v>
+        <v>19</v>
       </c>
       <c r="I78" t="s">
-        <v>244</v>
+        <v>26</v>
       </c>
       <c r="J78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -2818,36 +2818,36 @@
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C80" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D80" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E80" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F80" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G80" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H80" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="I80" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="J80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -2855,36 +2855,36 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C82" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D82" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E82" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F82" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G82" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H82" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="I82" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="J82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -2892,36 +2892,36 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>257</v>
+        <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>257</v>
+        <v>88</v>
       </c>
       <c r="D84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E84" t="s">
-        <v>257</v>
+        <v>88</v>
       </c>
       <c r="F84" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G84" t="s">
-        <v>261</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="I84" t="s">
-        <v>262</v>
+        <v>41</v>
       </c>
       <c r="J84" t="s">
-        <v>263</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -2929,36 +2929,36 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H86" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I86" t="s">
-        <v>269</v>
+        <v>159</v>
       </c>
       <c r="J86" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -2966,36 +2966,36 @@
         <v>44</v>
       </c>
       <c r="B88" t="s">
+        <v>100</v>
+      </c>
+      <c r="C88" t="s">
+        <v>100</v>
+      </c>
+      <c r="D88" t="s">
         <v>270</v>
       </c>
-      <c r="C88" t="s">
-        <v>270</v>
-      </c>
-      <c r="D88" t="s">
-        <v>272</v>
-      </c>
       <c r="E88" t="s">
-        <v>270</v>
+        <v>100</v>
       </c>
       <c r="F88" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G88" t="s">
-        <v>274</v>
+        <v>102</v>
       </c>
       <c r="H88" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I88" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="J88" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>271</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -3003,36 +3003,36 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
+        <v>272</v>
+      </c>
+      <c r="C90" t="s">
+        <v>272</v>
+      </c>
+      <c r="D90" t="s">
+        <v>274</v>
+      </c>
+      <c r="E90" t="s">
+        <v>272</v>
+      </c>
+      <c r="F90" t="s">
         <v>275</v>
       </c>
-      <c r="C90" t="s">
-        <v>275</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="G90" t="s">
+        <v>276</v>
+      </c>
+      <c r="H90" t="s">
+        <v>30</v>
+      </c>
+      <c r="I90" t="s">
         <v>277</v>
       </c>
-      <c r="E90" t="s">
-        <v>275</v>
-      </c>
-      <c r="F90" t="s">
-        <v>278</v>
-      </c>
-      <c r="G90" t="s">
-        <v>279</v>
-      </c>
-      <c r="H90" t="s">
-        <v>21</v>
-      </c>
-      <c r="I90" t="s">
-        <v>280</v>
-      </c>
       <c r="J90" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -3040,36 +3040,36 @@
         <v>46</v>
       </c>
       <c r="B92" t="s">
+        <v>278</v>
+      </c>
+      <c r="C92" t="s">
+        <v>278</v>
+      </c>
+      <c r="D92" t="s">
+        <v>280</v>
+      </c>
+      <c r="E92" t="s">
+        <v>278</v>
+      </c>
+      <c r="F92" t="s">
         <v>281</v>
       </c>
-      <c r="C92" t="s">
-        <v>281</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="G92" t="s">
+        <v>282</v>
+      </c>
+      <c r="H92" t="s">
+        <v>30</v>
+      </c>
+      <c r="I92" t="s">
         <v>283</v>
       </c>
-      <c r="E92" t="s">
-        <v>281</v>
-      </c>
-      <c r="F92" t="s">
-        <v>284</v>
-      </c>
-      <c r="G92" t="s">
-        <v>153</v>
-      </c>
-      <c r="H92" t="s">
-        <v>21</v>
-      </c>
-      <c r="I92" t="s">
-        <v>62</v>
-      </c>
       <c r="J92" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -3077,36 +3077,36 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C94" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D94" t="s">
+        <v>286</v>
+      </c>
+      <c r="E94" t="s">
+        <v>284</v>
+      </c>
+      <c r="F94" t="s">
         <v>287</v>
       </c>
-      <c r="E94" t="s">
-        <v>285</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>288</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
+        <v>45</v>
+      </c>
+      <c r="I94" t="s">
         <v>289</v>
       </c>
-      <c r="H94" t="s">
-        <v>29</v>
-      </c>
-      <c r="I94" t="s">
-        <v>290</v>
-      </c>
       <c r="J94" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -3114,36 +3114,36 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C96" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D96" t="s">
+        <v>292</v>
+      </c>
+      <c r="E96" t="s">
+        <v>290</v>
+      </c>
+      <c r="F96" t="s">
         <v>293</v>
       </c>
-      <c r="E96" t="s">
-        <v>291</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>294</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
+        <v>14</v>
+      </c>
+      <c r="I96" t="s">
         <v>295</v>
       </c>
-      <c r="H96" t="s">
-        <v>178</v>
-      </c>
-      <c r="I96" t="s">
-        <v>296</v>
-      </c>
       <c r="J96" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -3151,36 +3151,36 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C98" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D98" t="s">
+        <v>298</v>
+      </c>
+      <c r="E98" t="s">
+        <v>296</v>
+      </c>
+      <c r="F98" t="s">
         <v>299</v>
       </c>
-      <c r="E98" t="s">
-        <v>297</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>300</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" t="s">
         <v>301</v>
       </c>
-      <c r="H98" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98" t="s">
-        <v>60</v>
-      </c>
       <c r="J98" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -3206,7 +3206,7 @@
         <v>306</v>
       </c>
       <c r="H100" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="I100" t="s">
         <v>307</v>

--- a/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C338B980-6F2D-4BA9-9AC7-1251737CCD82}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA265CE3-C22E-494D-86CD-DAE277E80B1D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5AC1432C-0454-491C-B311-8CBC9194BD16}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="305">
   <si>
     <t>Symbol</t>
   </si>
@@ -140,12 +140,6 @@
     <t>PDEX</t>
   </si>
   <si>
-    <t>-3.39</t>
-  </si>
-  <si>
-    <t>7.00</t>
-  </si>
-  <si>
     <t>-2.63</t>
   </si>
   <si>
@@ -230,21 +224,12 @@
     <t>UHS</t>
   </si>
   <si>
-    <t>3.19</t>
-  </si>
-  <si>
     <t>Astellas Pharma Inc.</t>
   </si>
   <si>
     <t>4503.T</t>
   </si>
   <si>
-    <t>2.29</t>
-  </si>
-  <si>
-    <t>-2.19</t>
-  </si>
-  <si>
     <t>Exelixis, Inc.</t>
   </si>
   <si>
@@ -263,18 +248,9 @@
     <t>7733.T</t>
   </si>
   <si>
-    <t>BioMarin Pharmaceutical Inc.</t>
-  </si>
-  <si>
-    <t>BMRN</t>
-  </si>
-  <si>
     <t>5.73</t>
   </si>
   <si>
-    <t>-3.95</t>
-  </si>
-  <si>
     <t>Sun Pharmaceutical Industries Limited</t>
   </si>
   <si>
@@ -320,24 +296,9 @@
     <t>HLN.L</t>
   </si>
   <si>
-    <t>3.04</t>
-  </si>
-  <si>
     <t>-2.50</t>
   </si>
   <si>
-    <t>AnaptysBio, Inc.</t>
-  </si>
-  <si>
-    <t>ANAB</t>
-  </si>
-  <si>
-    <t>1.61</t>
-  </si>
-  <si>
-    <t>-3.96</t>
-  </si>
-  <si>
     <t>Al Hammadi Company For Development and Investment</t>
   </si>
   <si>
@@ -356,12 +317,6 @@
     <t>ALGN</t>
   </si>
   <si>
-    <t>4.77</t>
-  </si>
-  <si>
-    <t>-2.52</t>
-  </si>
-  <si>
     <t>Edwards Lifesciences Corporation</t>
   </si>
   <si>
@@ -392,33 +347,12 @@
     <t>-2.29</t>
   </si>
   <si>
-    <t>Hologic, Inc.</t>
-  </si>
-  <si>
-    <t>HOLX</t>
-  </si>
-  <si>
-    <t>17.06B</t>
-  </si>
-  <si>
-    <t>-5.14</t>
-  </si>
-  <si>
-    <t>4.18</t>
-  </si>
-  <si>
     <t>WuXi Biologics (Cayman) Inc.</t>
   </si>
   <si>
     <t>2269.HK</t>
   </si>
   <si>
-    <t>17.22B</t>
-  </si>
-  <si>
-    <t>+82.19</t>
-  </si>
-  <si>
     <t>8.13</t>
   </si>
   <si>
@@ -428,36 +362,18 @@
     <t>4164.SR</t>
   </si>
   <si>
-    <t>3.60B</t>
-  </si>
-  <si>
-    <t>+73.87</t>
-  </si>
-  <si>
     <t>4.64</t>
   </si>
   <si>
     <t>-3.43</t>
   </si>
   <si>
-    <t>13.25B</t>
-  </si>
-  <si>
-    <t>+72.27</t>
-  </si>
-  <si>
     <t>Mouwasat Medical Services Company</t>
   </si>
   <si>
     <t>4002.SR</t>
   </si>
   <si>
-    <t>3.69B</t>
-  </si>
-  <si>
-    <t>+65.20</t>
-  </si>
-  <si>
     <t>6.36</t>
   </si>
   <si>
@@ -467,240 +383,60 @@
     <t>9.57B</t>
   </si>
   <si>
-    <t>+55.64</t>
-  </si>
-  <si>
-    <t>13.57B</t>
-  </si>
-  <si>
-    <t>+51.83</t>
-  </si>
-  <si>
-    <t>7.83B</t>
-  </si>
-  <si>
-    <t>+64.61</t>
-  </si>
-  <si>
-    <t>783.90M</t>
-  </si>
-  <si>
-    <t>+43.00</t>
-  </si>
-  <si>
-    <t>562.08M</t>
-  </si>
-  <si>
-    <t>+40.23</t>
-  </si>
-  <si>
-    <t>1.03B</t>
-  </si>
-  <si>
-    <t>+18.65</t>
-  </si>
-  <si>
     <t>Lonza Group AG</t>
   </si>
   <si>
     <t>LONN.SW</t>
   </si>
   <si>
-    <t>42.90B</t>
-  </si>
-  <si>
-    <t>+18.13</t>
-  </si>
-  <si>
     <t>3.88</t>
   </si>
   <si>
     <t>-2.56</t>
   </si>
   <si>
-    <t>10.56B</t>
-  </si>
-  <si>
-    <t>+33.94</t>
-  </si>
-  <si>
     <t>3.66</t>
   </si>
   <si>
     <t>-2.51</t>
   </si>
   <si>
-    <t>29.02B</t>
-  </si>
-  <si>
-    <t>+134.38</t>
-  </si>
-  <si>
-    <t>11.09B</t>
-  </si>
-  <si>
-    <t>+54.98</t>
-  </si>
-  <si>
-    <t>27.74B</t>
-  </si>
-  <si>
-    <t>+37.37</t>
-  </si>
-  <si>
-    <t>41.24B</t>
-  </si>
-  <si>
-    <t>+54.09</t>
-  </si>
-  <si>
-    <t>12.20B</t>
-  </si>
-  <si>
-    <t>+26.23</t>
-  </si>
-  <si>
     <t>43.05B</t>
   </si>
   <si>
-    <t>+25.35</t>
-  </si>
-  <si>
-    <t>WuXi AppTec Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2359.HK</t>
-  </si>
-  <si>
-    <t>45.10B</t>
-  </si>
-  <si>
-    <t>+24.65</t>
-  </si>
-  <si>
-    <t>8.21</t>
-  </si>
-  <si>
-    <t>-3.37</t>
-  </si>
-  <si>
     <t>IDEXX Laboratories, Inc.</t>
   </si>
   <si>
     <t>IDXX</t>
   </si>
   <si>
-    <t>45.33B</t>
-  </si>
-  <si>
-    <t>+14.33</t>
-  </si>
-  <si>
     <t>23.99</t>
   </si>
   <si>
-    <t>13.75B</t>
-  </si>
-  <si>
-    <t>+10.17</t>
-  </si>
-  <si>
-    <t>160.14M</t>
-  </si>
-  <si>
-    <t>+8.07</t>
-  </si>
-  <si>
-    <t>48.74B</t>
-  </si>
-  <si>
-    <t>+7.88</t>
-  </si>
-  <si>
     <t>-3.52</t>
   </si>
   <si>
-    <t>51.83B</t>
-  </si>
-  <si>
-    <t>+42.04</t>
-  </si>
-  <si>
     <t>Abbott Laboratories</t>
   </si>
   <si>
     <t>ABT</t>
   </si>
   <si>
-    <t>159.20B</t>
-  </si>
-  <si>
-    <t>+27.64</t>
-  </si>
-  <si>
     <t>5.62</t>
   </si>
   <si>
     <t>-3.62</t>
   </si>
   <si>
-    <t>Ginkgo Bioworks Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>DNA</t>
-  </si>
-  <si>
-    <t>436.45M</t>
-  </si>
-  <si>
-    <t>+7.12</t>
-  </si>
-  <si>
-    <t>-7.61</t>
-  </si>
-  <si>
-    <t>169.29M</t>
-  </si>
-  <si>
-    <t>-0.98</t>
-  </si>
-  <si>
     <t>Healthcare Services Group, Inc.</t>
   </si>
   <si>
     <t>HCSG</t>
   </si>
   <si>
-    <t>1.57B</t>
-  </si>
-  <si>
-    <t>-14.41</t>
-  </si>
-  <si>
     <t>6.94</t>
   </si>
   <si>
-    <t>1.59B</t>
-  </si>
-  <si>
-    <t>+61.86</t>
-  </si>
-  <si>
-    <t>HOYA Corporation</t>
-  </si>
-  <si>
-    <t>7741.T</t>
-  </si>
-  <si>
-    <t>60.73B</t>
-  </si>
-  <si>
-    <t>-7.43</t>
-  </si>
-  <si>
-    <t>21.73</t>
-  </si>
-  <si>
     <t>-2.30</t>
   </si>
   <si>
@@ -710,256 +446,511 @@
     <t>HRMY</t>
   </si>
   <si>
-    <t>1.77B</t>
-  </si>
-  <si>
-    <t>+50.84</t>
-  </si>
-  <si>
-    <t>13.30B</t>
-  </si>
-  <si>
-    <t>+31.14</t>
-  </si>
-  <si>
     <t>Centene Corporation</t>
   </si>
   <si>
     <t>CNC</t>
   </si>
   <si>
-    <t>20.54B</t>
-  </si>
-  <si>
-    <t>+52.63</t>
-  </si>
-  <si>
-    <t>2.77</t>
-  </si>
-  <si>
-    <t>-2.81</t>
-  </si>
-  <si>
-    <t>1.64B</t>
-  </si>
-  <si>
-    <t>+168.22</t>
-  </si>
-  <si>
-    <t>162.22B</t>
-  </si>
-  <si>
-    <t>+126.99</t>
-  </si>
-  <si>
     <t>Sanofi</t>
   </si>
   <si>
     <t>SAN.PA</t>
   </si>
   <si>
-    <t>113.01B</t>
-  </si>
-  <si>
-    <t>+64.89</t>
-  </si>
-  <si>
-    <t>1.84</t>
-  </si>
-  <si>
-    <t>-2.58</t>
-  </si>
-  <si>
-    <t>10.20B</t>
-  </si>
-  <si>
-    <t>+90.54</t>
-  </si>
-  <si>
-    <t>Neurocrine Biosciences, Inc.</t>
-  </si>
-  <si>
-    <t>NBIX</t>
-  </si>
-  <si>
-    <t>12.70B</t>
-  </si>
-  <si>
-    <t>+57.39</t>
-  </si>
-  <si>
-    <t>7.80</t>
-  </si>
-  <si>
-    <t>Madrigal Pharmaceuticals, Inc.</t>
-  </si>
-  <si>
-    <t>MDGL</t>
-  </si>
-  <si>
-    <t>11.50B</t>
-  </si>
-  <si>
-    <t>+56.11</t>
-  </si>
-  <si>
-    <t>21.16</t>
-  </si>
-  <si>
-    <t>-1.85</t>
-  </si>
-  <si>
-    <t>Pro Medicus Limited</t>
-  </si>
-  <si>
-    <t>PME.AX</t>
-  </si>
-  <si>
-    <t>10.33B</t>
-  </si>
-  <si>
-    <t>+55.28</t>
-  </si>
-  <si>
-    <t>98.62</t>
-  </si>
-  <si>
-    <t>-0.59</t>
-  </si>
-  <si>
-    <t>12.82B</t>
-  </si>
-  <si>
-    <t>+47.65</t>
-  </si>
-  <si>
     <t>Medpace Holdings, Inc.</t>
   </si>
   <si>
     <t>MEDP</t>
   </si>
   <si>
-    <t>11.68B</t>
-  </si>
-  <si>
-    <t>+32.37</t>
-  </si>
-  <si>
     <t>7.14</t>
   </si>
   <si>
-    <t>1.10B</t>
-  </si>
-  <si>
-    <t>+35.31</t>
-  </si>
-  <si>
-    <t>LifeStance Health Group, Inc.</t>
-  </si>
-  <si>
-    <t>LFST</t>
-  </si>
-  <si>
-    <t>2.72B</t>
-  </si>
-  <si>
-    <t>+71.06</t>
-  </si>
-  <si>
-    <t>2.65</t>
-  </si>
-  <si>
-    <t>-3.15</t>
-  </si>
-  <si>
-    <t>Dallah Healthcare Company</t>
-  </si>
-  <si>
-    <t>4004.SR</t>
-  </si>
-  <si>
-    <t>3.30B</t>
-  </si>
-  <si>
-    <t>+61.95</t>
-  </si>
-  <si>
-    <t>3.93</t>
-  </si>
-  <si>
-    <t>-3.38</t>
-  </si>
-  <si>
-    <t>Bavarian Nordic A/S</t>
-  </si>
-  <si>
-    <t>BAVA.CO</t>
-  </si>
-  <si>
-    <t>2.28B</t>
-  </si>
-  <si>
-    <t>+45.67</t>
-  </si>
-  <si>
-    <t>6.46</t>
-  </si>
-  <si>
-    <t>-3.01</t>
-  </si>
-  <si>
     <t>Tenet Healthcare Corporation</t>
   </si>
   <si>
     <t>THC</t>
   </si>
   <si>
-    <t>16.42B</t>
-  </si>
-  <si>
-    <t>+39.33</t>
-  </si>
-  <si>
-    <t>1.98</t>
-  </si>
-  <si>
-    <t>-2.47</t>
-  </si>
-  <si>
-    <t>Prestige Consumer Healthcare Inc.</t>
-  </si>
-  <si>
-    <t>PBH</t>
-  </si>
-  <si>
-    <t>2.82B</t>
-  </si>
-  <si>
-    <t>+35.63</t>
-  </si>
-  <si>
-    <t>2.46</t>
-  </si>
-  <si>
-    <t>-2.22</t>
-  </si>
-  <si>
     <t>Option Care Health, Inc.</t>
   </si>
   <si>
     <t>OPCH</t>
   </si>
   <si>
-    <t>4.49B</t>
-  </si>
-  <si>
-    <t>+34.15</t>
-  </si>
-  <si>
     <t>3.53</t>
   </si>
   <si>
     <t>-2.46</t>
+  </si>
+  <si>
+    <t>160.90B</t>
+  </si>
+  <si>
+    <t>+125.26</t>
+  </si>
+  <si>
+    <t>156.26B</t>
+  </si>
+  <si>
+    <t>+22.35</t>
+  </si>
+  <si>
+    <t>112.91B</t>
+  </si>
+  <si>
+    <t>+64.16</t>
+  </si>
+  <si>
+    <t>1.93</t>
+  </si>
+  <si>
+    <t>-1.64</t>
+  </si>
+  <si>
+    <t>Regeneron Pharmaceuticals, Inc.</t>
+  </si>
+  <si>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>73.43B</t>
+  </si>
+  <si>
+    <t>+7.48</t>
+  </si>
+  <si>
+    <t>18.37</t>
+  </si>
+  <si>
+    <t>-2.69</t>
+  </si>
+  <si>
+    <t>50.89B</t>
+  </si>
+  <si>
+    <t>+43.08</t>
+  </si>
+  <si>
+    <t>47.93B</t>
+  </si>
+  <si>
+    <t>+12.45</t>
+  </si>
+  <si>
+    <t>45.74B</t>
+  </si>
+  <si>
+    <t>+39.98</t>
+  </si>
+  <si>
+    <t>44.81B</t>
+  </si>
+  <si>
+    <t>+15.52</t>
+  </si>
+  <si>
+    <t>+15.29</t>
+  </si>
+  <si>
+    <t>13.21B</t>
+  </si>
+  <si>
+    <t>+72.96</t>
+  </si>
+  <si>
+    <t>+55.84</t>
+  </si>
+  <si>
+    <t>11.04B</t>
+  </si>
+  <si>
+    <t>+32.17</t>
+  </si>
+  <si>
+    <t>11.88B</t>
+  </si>
+  <si>
+    <t>+31.44</t>
+  </si>
+  <si>
+    <t>10.78B</t>
+  </si>
+  <si>
+    <t>+14.84</t>
+  </si>
+  <si>
+    <t>-3.29</t>
+  </si>
+  <si>
+    <t>Molina Healthcare, Inc.</t>
+  </si>
+  <si>
+    <t>MOH</t>
+  </si>
+  <si>
+    <t>9.89B</t>
+  </si>
+  <si>
+    <t>+7.05</t>
+  </si>
+  <si>
+    <t>3.85</t>
+  </si>
+  <si>
+    <t>-4.20</t>
+  </si>
+  <si>
+    <t>12.09B</t>
+  </si>
+  <si>
+    <t>+58.49</t>
+  </si>
+  <si>
+    <t>16.98B</t>
+  </si>
+  <si>
+    <t>+42.95</t>
+  </si>
+  <si>
+    <t>41.54B</t>
+  </si>
+  <si>
+    <t>+25.44</t>
+  </si>
+  <si>
+    <t>3.02</t>
+  </si>
+  <si>
+    <t>+21.96</t>
+  </si>
+  <si>
+    <t>13.45B</t>
+  </si>
+  <si>
+    <t>+16.52</t>
+  </si>
+  <si>
+    <t>1.50B</t>
+  </si>
+  <si>
+    <t>-4.87</t>
+  </si>
+  <si>
+    <t>NeoGenomics, Inc.</t>
+  </si>
+  <si>
+    <t>NEO</t>
+  </si>
+  <si>
+    <t>46.91M</t>
+  </si>
+  <si>
+    <t>+240.20</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>-2.59</t>
+  </si>
+  <si>
+    <t>1.54B</t>
+  </si>
+  <si>
+    <t>+65.66</t>
+  </si>
+  <si>
+    <t>Amphastar Pharmaceuticals, Inc.</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>1.01B</t>
+  </si>
+  <si>
+    <t>+65.02</t>
+  </si>
+  <si>
+    <t>2.54</t>
+  </si>
+  <si>
+    <t>-2.20</t>
+  </si>
+  <si>
+    <t>Ardent Health Partners, LLC</t>
+  </si>
+  <si>
+    <t>ARDT</t>
+  </si>
+  <si>
+    <t>1.41B</t>
+  </si>
+  <si>
+    <t>+67.91</t>
+  </si>
+  <si>
+    <t>1.94</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>1.79B</t>
+  </si>
+  <si>
+    <t>+54.78</t>
+  </si>
+  <si>
+    <t>809.90M</t>
+  </si>
+  <si>
+    <t>+43.45</t>
+  </si>
+  <si>
+    <t>569.75M</t>
+  </si>
+  <si>
+    <t>+40.36</t>
+  </si>
+  <si>
+    <t>13.06B</t>
+  </si>
+  <si>
+    <t>+31.75</t>
+  </si>
+  <si>
+    <t>138.94M</t>
+  </si>
+  <si>
+    <t>+22.16</t>
+  </si>
+  <si>
+    <t>30.90B</t>
+  </si>
+  <si>
+    <t>+120.15</t>
+  </si>
+  <si>
+    <t>3.12B</t>
+  </si>
+  <si>
+    <t>+72.11</t>
+  </si>
+  <si>
+    <t>3.41</t>
+  </si>
+  <si>
+    <t>3.64B</t>
+  </si>
+  <si>
+    <t>+71.97</t>
+  </si>
+  <si>
+    <t>25.22B</t>
+  </si>
+  <si>
+    <t>+52.26</t>
+  </si>
+  <si>
+    <t>2.97</t>
+  </si>
+  <si>
+    <t>-2.79</t>
+  </si>
+  <si>
+    <t>16.14B</t>
+  </si>
+  <si>
+    <t>+28.59</t>
+  </si>
+  <si>
+    <t>1.85</t>
+  </si>
+  <si>
+    <t>26.60B</t>
+  </si>
+  <si>
+    <t>+28.10</t>
+  </si>
+  <si>
+    <t>2.55</t>
+  </si>
+  <si>
+    <t>-3.89</t>
+  </si>
+  <si>
+    <t>SI-BONE, Inc.</t>
+  </si>
+  <si>
+    <t>SIBN</t>
+  </si>
+  <si>
+    <t>540.58M</t>
+  </si>
+  <si>
+    <t>+36.50</t>
+  </si>
+  <si>
+    <t>7.29</t>
+  </si>
+  <si>
+    <t>-2.84</t>
+  </si>
+  <si>
+    <t>12.57B</t>
+  </si>
+  <si>
+    <t>+21.79</t>
+  </si>
+  <si>
+    <t>4.48</t>
+  </si>
+  <si>
+    <t>DexCom, Inc.</t>
+  </si>
+  <si>
+    <t>DXCM</t>
+  </si>
+  <si>
+    <t>23.58B</t>
+  </si>
+  <si>
+    <t>+99.59</t>
+  </si>
+  <si>
+    <t>6.12</t>
+  </si>
+  <si>
+    <t>-2.92</t>
+  </si>
+  <si>
+    <t>7.51B</t>
+  </si>
+  <si>
+    <t>+70.45</t>
+  </si>
+  <si>
+    <t>3.63B</t>
+  </si>
+  <si>
+    <t>+64.12</t>
+  </si>
+  <si>
+    <t>Middle East Pharmaceutical Industries Company</t>
+  </si>
+  <si>
+    <t>4016.SR</t>
+  </si>
+  <si>
+    <t>546.67M</t>
+  </si>
+  <si>
+    <t>+31.02</t>
+  </si>
+  <si>
+    <t>9.74</t>
+  </si>
+  <si>
+    <t>Kyowa Kirin Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4151.T</t>
+  </si>
+  <si>
+    <t>8.00B</t>
+  </si>
+  <si>
+    <t>+26.43</t>
+  </si>
+  <si>
+    <t>5.28</t>
+  </si>
+  <si>
+    <t>-2.15</t>
+  </si>
+  <si>
+    <t>Chemed Corporation</t>
+  </si>
+  <si>
+    <t>CHE</t>
+  </si>
+  <si>
+    <t>5.78B</t>
+  </si>
+  <si>
+    <t>+23.55</t>
+  </si>
+  <si>
+    <t>9.57</t>
+  </si>
+  <si>
+    <t>-2.72</t>
+  </si>
+  <si>
+    <t>145.73M</t>
+  </si>
+  <si>
+    <t>+20.14</t>
+  </si>
+  <si>
+    <t>HealthStream, Inc.</t>
+  </si>
+  <si>
+    <t>HSTM</t>
+  </si>
+  <si>
+    <t>624.67M</t>
+  </si>
+  <si>
+    <t>+16.00</t>
+  </si>
+  <si>
+    <t>-2.45</t>
+  </si>
+  <si>
+    <t>1.06B</t>
+  </si>
+  <si>
+    <t>+15.60</t>
+  </si>
+  <si>
+    <t>1.12B</t>
+  </si>
+  <si>
+    <t>+32.04</t>
+  </si>
+  <si>
+    <t>Eisai Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4523.T</t>
+  </si>
+  <si>
+    <t>8.48B</t>
+  </si>
+  <si>
+    <t>+6.88</t>
+  </si>
+  <si>
+    <t>2.85</t>
+  </si>
+  <si>
+    <t>Laboratorios Farmaceuticos Rovi, S.A.</t>
+  </si>
+  <si>
+    <t>ROVI.MC</t>
+  </si>
+  <si>
+    <t>4.77B</t>
+  </si>
+  <si>
+    <t>-10.16</t>
+  </si>
+  <si>
+    <t>9.75</t>
   </si>
 </sst>
 </file>
@@ -1012,6 +1003,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1375,28 +1370,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="G2" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -1404,7 +1399,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1412,28 +1407,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="G4" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
@@ -1441,7 +1436,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1449,28 +1444,28 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
@@ -1478,7 +1473,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1486,28 +1481,28 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="G8" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
@@ -1515,7 +1510,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1523,28 +1518,28 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
@@ -1552,7 +1547,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1560,28 +1555,28 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="F12" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>186</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -1589,7 +1584,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>52</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1597,36 +1592,36 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1634,28 +1629,28 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="H16" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
@@ -1663,7 +1658,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1671,28 +1666,28 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
+        <v>194</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
@@ -1700,7 +1695,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1708,28 +1703,28 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" t="s">
         <v>152</v>
       </c>
-      <c r="E20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" t="s">
-        <v>153</v>
-      </c>
       <c r="G20" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
@@ -1737,7 +1732,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1745,28 +1740,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E22" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="F22" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G22" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="H22" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
@@ -1774,7 +1769,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1782,28 +1777,28 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="F24" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="G24" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="H24" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="I24" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
@@ -1811,7 +1806,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>74</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1819,28 +1814,28 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I26" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
@@ -1848,7 +1843,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1856,28 +1851,28 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="E28" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I28" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
@@ -1885,7 +1880,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1893,28 +1888,28 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="F30" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="G30" t="s">
-        <v>67</v>
+        <v>204</v>
       </c>
       <c r="H30" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>68</v>
+        <v>205</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -1922,7 +1917,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1930,36 +1925,36 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="E32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="G32" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J32" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1967,28 +1962,28 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="F34" t="s">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="G34" t="s">
-        <v>71</v>
+        <v>212</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="I34" t="s">
-        <v>72</v>
+        <v>213</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
@@ -1996,7 +1991,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>70</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2004,28 +1999,28 @@
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>214</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>214</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="E36" t="s">
-        <v>92</v>
+        <v>214</v>
       </c>
       <c r="F36" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="I36" t="s">
-        <v>95</v>
+        <v>219</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
@@ -2033,7 +2028,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>93</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2041,28 +2036,28 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="E38" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="F38" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="G38" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="H38" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="I38" t="s">
-        <v>181</v>
+        <v>102</v>
       </c>
       <c r="J38" t="s">
         <v>15</v>
@@ -2070,7 +2065,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2078,28 +2073,28 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="E40" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="G40" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="H40" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I40" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="J40" t="s">
         <v>15</v>
@@ -2107,7 +2102,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>183</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2115,28 +2110,28 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="E42" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="G42" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="H42" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I42" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="J42" t="s">
         <v>15</v>
@@ -2144,7 +2139,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>105</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2152,28 +2147,28 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="F44" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="G44" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="H44" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="I44" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="J44" t="s">
         <v>15</v>
@@ -2181,7 +2176,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2189,28 +2184,28 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="E46" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="F46" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="G46" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="H46" t="s">
         <v>14</v>
       </c>
       <c r="I46" t="s">
-        <v>193</v>
+        <v>38</v>
       </c>
       <c r="J46" t="s">
         <v>15</v>
@@ -2218,7 +2213,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2226,28 +2221,28 @@
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
       <c r="E48" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F48" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="G48" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="H48" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I48" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="J48" t="s">
         <v>15</v>
@@ -2255,7 +2250,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2263,28 +2258,28 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>196</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>196</v>
+        <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="E50" t="s">
-        <v>196</v>
+        <v>56</v>
       </c>
       <c r="F50" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="G50" t="s">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="H50" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I50" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="J50" t="s">
         <v>15</v>
@@ -2292,7 +2287,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>197</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -2300,28 +2295,28 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="D52" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="E52" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="F52" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="G52" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="H52" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="I52" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="J52" t="s">
         <v>15</v>
@@ -2329,7 +2324,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -2337,28 +2332,28 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="C54" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="D54" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="F54" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I54" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="J54" t="s">
         <v>15</v>
@@ -2366,7 +2361,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -2374,28 +2369,28 @@
         <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="E56" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="F56" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="G56" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="H56" t="s">
         <v>30</v>
       </c>
       <c r="I56" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="J56" t="s">
         <v>15</v>
@@ -2403,7 +2398,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>210</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -2411,28 +2406,28 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="C58" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D58" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="E58" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="F58" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="G58" t="s">
-        <v>85</v>
+        <v>243</v>
       </c>
       <c r="H58" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I58" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="J58" t="s">
         <v>15</v>
@@ -2440,7 +2435,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -2448,28 +2443,28 @@
         <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>216</v>
+        <v>136</v>
       </c>
       <c r="C60" t="s">
-        <v>216</v>
+        <v>136</v>
       </c>
       <c r="D60" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="E60" t="s">
-        <v>216</v>
+        <v>136</v>
       </c>
       <c r="F60" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="G60" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="H60" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I60" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="J60" t="s">
         <v>15</v>
@@ -2477,7 +2472,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -2485,36 +2480,36 @@
         <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="C62" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="D62" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="E62" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="F62" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G62" t="s">
-        <v>53</v>
+        <v>252</v>
       </c>
       <c r="H62" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="I62" t="s">
-        <v>117</v>
+        <v>253</v>
       </c>
       <c r="J62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -2522,28 +2517,28 @@
         <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="C64" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D64" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="F64" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="G64" t="s">
-        <v>116</v>
+        <v>256</v>
       </c>
       <c r="H64" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="I64" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="J64" t="s">
         <v>15</v>
@@ -2551,7 +2546,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -2559,28 +2554,28 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="C66" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="D66" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="E66" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="F66" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="H66" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I66" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="J66" t="s">
         <v>15</v>
@@ -2588,7 +2583,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2596,36 +2591,36 @@
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>228</v>
+        <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>228</v>
+        <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>230</v>
+        <v>149</v>
       </c>
       <c r="E68" t="s">
-        <v>228</v>
+        <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="G68" t="s">
-        <v>232</v>
+        <v>10</v>
       </c>
       <c r="H68" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I68" t="s">
-        <v>233</v>
+        <v>12</v>
       </c>
       <c r="J68" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>229</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -2633,28 +2628,28 @@
         <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>257</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
+        <v>257</v>
       </c>
       <c r="D70" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="E70" t="s">
-        <v>96</v>
+        <v>257</v>
       </c>
       <c r="F70" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="G70" t="s">
-        <v>98</v>
+        <v>261</v>
       </c>
       <c r="H70" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I70" t="s">
-        <v>99</v>
+        <v>262</v>
       </c>
       <c r="J70" t="s">
         <v>13</v>
@@ -2662,7 +2657,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -2670,36 +2665,36 @@
         <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="D72" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="E72" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="F72" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="G72" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="H72" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I72" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J72" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -2707,28 +2702,28 @@
         <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>238</v>
+        <v>138</v>
       </c>
       <c r="C74" t="s">
-        <v>238</v>
+        <v>138</v>
       </c>
       <c r="D74" t="s">
-        <v>240</v>
+        <v>153</v>
       </c>
       <c r="E74" t="s">
-        <v>238</v>
+        <v>138</v>
       </c>
       <c r="F74" t="s">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="G74" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="H74" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I74" t="s">
-        <v>243</v>
+        <v>156</v>
       </c>
       <c r="J74" t="s">
         <v>15</v>
@@ -2736,7 +2731,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>239</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -2744,28 +2739,28 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C76" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D76" t="s">
-        <v>244</v>
+        <v>167</v>
       </c>
       <c r="E76" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F76" t="s">
-        <v>245</v>
+        <v>168</v>
       </c>
       <c r="G76" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H76" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="I76" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J76" t="s">
         <v>13</v>
@@ -2773,7 +2768,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -2781,36 +2776,36 @@
         <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>246</v>
+        <v>93</v>
       </c>
       <c r="C78" t="s">
-        <v>246</v>
+        <v>93</v>
       </c>
       <c r="D78" t="s">
-        <v>248</v>
+        <v>165</v>
       </c>
       <c r="E78" t="s">
-        <v>246</v>
+        <v>93</v>
       </c>
       <c r="F78" t="s">
-        <v>249</v>
+        <v>166</v>
       </c>
       <c r="G78" t="s">
-        <v>250</v>
+        <v>96</v>
       </c>
       <c r="H78" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I78" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="J78" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>247</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -2818,36 +2813,36 @@
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>251</v>
+        <v>110</v>
       </c>
       <c r="C80" t="s">
-        <v>251</v>
+        <v>110</v>
       </c>
       <c r="D80" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E80" t="s">
-        <v>251</v>
+        <v>110</v>
       </c>
       <c r="F80" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="G80" t="s">
-        <v>255</v>
+        <v>112</v>
       </c>
       <c r="H80" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="I80" t="s">
-        <v>256</v>
+        <v>113</v>
       </c>
       <c r="J80" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>252</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -2855,36 +2850,36 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>257</v>
+        <v>97</v>
       </c>
       <c r="C82" t="s">
-        <v>257</v>
+        <v>97</v>
       </c>
       <c r="D82" t="s">
-        <v>259</v>
+        <v>163</v>
       </c>
       <c r="E82" t="s">
-        <v>257</v>
+        <v>97</v>
       </c>
       <c r="F82" t="s">
-        <v>260</v>
+        <v>164</v>
       </c>
       <c r="G82" t="s">
-        <v>261</v>
+        <v>70</v>
       </c>
       <c r="H82" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="I82" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="J82" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>258</v>
+        <v>98</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -2892,28 +2887,28 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>267</v>
       </c>
       <c r="C84" t="s">
-        <v>88</v>
+        <v>267</v>
       </c>
       <c r="D84" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E84" t="s">
-        <v>88</v>
+        <v>267</v>
       </c>
       <c r="F84" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G84" t="s">
-        <v>90</v>
+        <v>271</v>
       </c>
       <c r="H84" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="I84" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="J84" t="s">
         <v>13</v>
@@ -2921,7 +2916,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>89</v>
+        <v>268</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -2929,28 +2924,28 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C86" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D86" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E86" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F86" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="G86" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="H86" t="s">
         <v>14</v>
       </c>
       <c r="I86" t="s">
-        <v>159</v>
+        <v>277</v>
       </c>
       <c r="J86" t="s">
         <v>15</v>
@@ -2958,7 +2953,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -2966,36 +2961,36 @@
         <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>278</v>
       </c>
       <c r="C88" t="s">
-        <v>100</v>
+        <v>278</v>
       </c>
       <c r="D88" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E88" t="s">
-        <v>100</v>
+        <v>278</v>
       </c>
       <c r="F88" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G88" t="s">
-        <v>102</v>
+        <v>282</v>
       </c>
       <c r="H88" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I88" t="s">
-        <v>103</v>
+        <v>283</v>
       </c>
       <c r="J88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>101</v>
+        <v>279</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -3003,36 +2998,36 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>272</v>
+        <v>32</v>
       </c>
       <c r="C90" t="s">
-        <v>272</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="E90" t="s">
-        <v>272</v>
+        <v>32</v>
       </c>
       <c r="F90" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="G90" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="H90" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I90" t="s">
         <v>277</v>
       </c>
       <c r="J90" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>273</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -3040,36 +3035,36 @@
         <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C92" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D92" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E92" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="F92" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="G92" t="s">
-        <v>282</v>
+        <v>147</v>
       </c>
       <c r="H92" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I92" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="J92" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -3077,36 +3072,36 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>284</v>
+        <v>27</v>
       </c>
       <c r="C94" t="s">
-        <v>284</v>
+        <v>27</v>
       </c>
       <c r="D94" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E94" t="s">
-        <v>284</v>
+        <v>27</v>
       </c>
       <c r="F94" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G94" t="s">
-        <v>288</v>
+        <v>29</v>
       </c>
       <c r="H94" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I94" t="s">
-        <v>289</v>
+        <v>31</v>
       </c>
       <c r="J94" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>285</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -3114,36 +3109,36 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>290</v>
+        <v>87</v>
       </c>
       <c r="C96" t="s">
-        <v>290</v>
+        <v>87</v>
       </c>
       <c r="D96" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E96" t="s">
-        <v>290</v>
+        <v>87</v>
       </c>
       <c r="F96" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G96" t="s">
-        <v>294</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I96" t="s">
-        <v>295</v>
+        <v>90</v>
       </c>
       <c r="J96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>291</v>
+        <v>88</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -3151,28 +3146,28 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C98" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D98" t="s">
+        <v>297</v>
+      </c>
+      <c r="E98" t="s">
+        <v>295</v>
+      </c>
+      <c r="F98" t="s">
         <v>298</v>
       </c>
-      <c r="E98" t="s">
-        <v>296</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>299</v>
-      </c>
-      <c r="G98" t="s">
-        <v>300</v>
       </c>
       <c r="H98" t="s">
         <v>14</v>
       </c>
       <c r="I98" t="s">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="J98" t="s">
         <v>15</v>
@@ -3180,7 +3175,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -3188,28 +3183,28 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
+        <v>300</v>
+      </c>
+      <c r="C100" t="s">
+        <v>300</v>
+      </c>
+      <c r="D100" t="s">
         <v>302</v>
       </c>
-      <c r="C100" t="s">
-        <v>302</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>300</v>
+      </c>
+      <c r="F100" t="s">
+        <v>303</v>
+      </c>
+      <c r="G100" t="s">
         <v>304</v>
       </c>
-      <c r="E100" t="s">
-        <v>302</v>
-      </c>
-      <c r="F100" t="s">
-        <v>305</v>
-      </c>
-      <c r="G100" t="s">
-        <v>306</v>
-      </c>
       <c r="H100" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I100" t="s">
-        <v>307</v>
+        <v>39</v>
       </c>
       <c r="J100" t="s">
         <v>15</v>
@@ -3217,7 +3212,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA265CE3-C22E-494D-86CD-DAE277E80B1D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AB806BD-F8C4-484E-A4C2-283C2039EADE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5AC1432C-0454-491C-B311-8CBC9194BD16}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="316">
   <si>
     <t>Symbol</t>
   </si>
@@ -119,21 +119,12 @@
     <t>-2.83</t>
   </si>
   <si>
-    <t>Collegium Pharmaceutical, Inc.</t>
-  </si>
-  <si>
-    <t>COLL</t>
-  </si>
-  <si>
     <t>1.58</t>
   </si>
   <si>
     <t>7.0</t>
   </si>
   <si>
-    <t>-2.90</t>
-  </si>
-  <si>
     <t>Pro-Dex, Inc.</t>
   </si>
   <si>
@@ -158,15 +149,6 @@
     <t>-2.71</t>
   </si>
   <si>
-    <t>Fresenius Medical Care AG &amp; Co. KGaA</t>
-  </si>
-  <si>
-    <t>FME.DE</t>
-  </si>
-  <si>
-    <t>1.31</t>
-  </si>
-  <si>
     <t>8.0</t>
   </si>
   <si>
@@ -206,18 +188,6 @@
     <t>3.91</t>
   </si>
   <si>
-    <t>Daiichi Sankyo Company, Limited</t>
-  </si>
-  <si>
-    <t>4568.T</t>
-  </si>
-  <si>
-    <t>3.63</t>
-  </si>
-  <si>
-    <t>-2.37</t>
-  </si>
-  <si>
     <t>Universal Health Services, Inc.</t>
   </si>
   <si>
@@ -251,18 +221,6 @@
     <t>5.73</t>
   </si>
   <si>
-    <t>Sun Pharmaceutical Industries Limited</t>
-  </si>
-  <si>
-    <t>SUNPHARMA.NS</t>
-  </si>
-  <si>
-    <t>15.35</t>
-  </si>
-  <si>
-    <t>-3.54</t>
-  </si>
-  <si>
     <t>Innoviva, Inc.</t>
   </si>
   <si>
@@ -287,9 +245,6 @@
     <t>11.29</t>
   </si>
   <si>
-    <t>2.0</t>
-  </si>
-  <si>
     <t>Haleon plc</t>
   </si>
   <si>
@@ -299,18 +254,6 @@
     <t>-2.50</t>
   </si>
   <si>
-    <t>Al Hammadi Company For Development and Investment</t>
-  </si>
-  <si>
-    <t>4007.SR</t>
-  </si>
-  <si>
-    <t>5.07</t>
-  </si>
-  <si>
-    <t>-3.26</t>
-  </si>
-  <si>
     <t>Align Technology, Inc.</t>
   </si>
   <si>
@@ -323,9 +266,6 @@
     <t>EW</t>
   </si>
   <si>
-    <t>-2.28</t>
-  </si>
-  <si>
     <t>11.63</t>
   </si>
   <si>
@@ -377,12 +317,6 @@
     <t>6.36</t>
   </si>
   <si>
-    <t>-3.24</t>
-  </si>
-  <si>
-    <t>9.57B</t>
-  </si>
-  <si>
     <t>Lonza Group AG</t>
   </si>
   <si>
@@ -398,36 +332,9 @@
     <t>3.66</t>
   </si>
   <si>
-    <t>-2.51</t>
-  </si>
-  <si>
-    <t>43.05B</t>
-  </si>
-  <si>
-    <t>IDEXX Laboratories, Inc.</t>
-  </si>
-  <si>
-    <t>IDXX</t>
-  </si>
-  <si>
-    <t>23.99</t>
-  </si>
-  <si>
     <t>-3.52</t>
   </si>
   <si>
-    <t>Abbott Laboratories</t>
-  </si>
-  <si>
-    <t>ABT</t>
-  </si>
-  <si>
-    <t>5.62</t>
-  </si>
-  <si>
-    <t>-3.62</t>
-  </si>
-  <si>
     <t>Healthcare Services Group, Inc.</t>
   </si>
   <si>
@@ -440,12 +347,6 @@
     <t>-2.30</t>
   </si>
   <si>
-    <t>Harmony Biosciences Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>HRMY</t>
-  </si>
-  <si>
     <t>Centene Corporation</t>
   </si>
   <si>
@@ -479,30 +380,9 @@
     <t>OPCH</t>
   </si>
   <si>
-    <t>3.53</t>
-  </si>
-  <si>
     <t>-2.46</t>
   </si>
   <si>
-    <t>160.90B</t>
-  </si>
-  <si>
-    <t>+125.26</t>
-  </si>
-  <si>
-    <t>156.26B</t>
-  </si>
-  <si>
-    <t>+22.35</t>
-  </si>
-  <si>
-    <t>112.91B</t>
-  </si>
-  <si>
-    <t>+64.16</t>
-  </si>
-  <si>
     <t>1.93</t>
   </si>
   <si>
@@ -515,72 +395,12 @@
     <t>REGN</t>
   </si>
   <si>
-    <t>73.43B</t>
-  </si>
-  <si>
-    <t>+7.48</t>
-  </si>
-  <si>
     <t>18.37</t>
   </si>
   <si>
     <t>-2.69</t>
   </si>
   <si>
-    <t>50.89B</t>
-  </si>
-  <si>
-    <t>+43.08</t>
-  </si>
-  <si>
-    <t>47.93B</t>
-  </si>
-  <si>
-    <t>+12.45</t>
-  </si>
-  <si>
-    <t>45.74B</t>
-  </si>
-  <si>
-    <t>+39.98</t>
-  </si>
-  <si>
-    <t>44.81B</t>
-  </si>
-  <si>
-    <t>+15.52</t>
-  </si>
-  <si>
-    <t>+15.29</t>
-  </si>
-  <si>
-    <t>13.21B</t>
-  </si>
-  <si>
-    <t>+72.96</t>
-  </si>
-  <si>
-    <t>+55.84</t>
-  </si>
-  <si>
-    <t>11.04B</t>
-  </si>
-  <si>
-    <t>+32.17</t>
-  </si>
-  <si>
-    <t>11.88B</t>
-  </si>
-  <si>
-    <t>+31.44</t>
-  </si>
-  <si>
-    <t>10.78B</t>
-  </si>
-  <si>
-    <t>+14.84</t>
-  </si>
-  <si>
     <t>-3.29</t>
   </si>
   <si>
@@ -590,90 +410,30 @@
     <t>MOH</t>
   </si>
   <si>
-    <t>9.89B</t>
-  </si>
-  <si>
-    <t>+7.05</t>
-  </si>
-  <si>
     <t>3.85</t>
   </si>
   <si>
     <t>-4.20</t>
   </si>
   <si>
-    <t>12.09B</t>
-  </si>
-  <si>
-    <t>+58.49</t>
-  </si>
-  <si>
-    <t>16.98B</t>
-  </si>
-  <si>
-    <t>+42.95</t>
-  </si>
-  <si>
-    <t>41.54B</t>
-  </si>
-  <si>
-    <t>+25.44</t>
-  </si>
-  <si>
-    <t>3.02</t>
-  </si>
-  <si>
-    <t>+21.96</t>
-  </si>
-  <si>
-    <t>13.45B</t>
-  </si>
-  <si>
-    <t>+16.52</t>
-  </si>
-  <si>
-    <t>1.50B</t>
-  </si>
-  <si>
-    <t>-4.87</t>
-  </si>
-  <si>
     <t>NeoGenomics, Inc.</t>
   </si>
   <si>
     <t>NEO</t>
   </si>
   <si>
-    <t>46.91M</t>
-  </si>
-  <si>
-    <t>+240.20</t>
-  </si>
-  <si>
     <t>0.35</t>
   </si>
   <si>
     <t>-2.59</t>
   </si>
   <si>
-    <t>1.54B</t>
-  </si>
-  <si>
-    <t>+65.66</t>
-  </si>
-  <si>
     <t>Amphastar Pharmaceuticals, Inc.</t>
   </si>
   <si>
     <t>AMPH</t>
   </si>
   <si>
-    <t>1.01B</t>
-  </si>
-  <si>
-    <t>+65.02</t>
-  </si>
-  <si>
     <t>2.54</t>
   </si>
   <si>
@@ -686,126 +446,30 @@
     <t>ARDT</t>
   </si>
   <si>
-    <t>1.41B</t>
-  </si>
-  <si>
-    <t>+67.91</t>
-  </si>
-  <si>
     <t>1.94</t>
   </si>
   <si>
     <t>0.92</t>
   </si>
   <si>
-    <t>1.79B</t>
-  </si>
-  <si>
-    <t>+54.78</t>
-  </si>
-  <si>
-    <t>809.90M</t>
-  </si>
-  <si>
-    <t>+43.45</t>
-  </si>
-  <si>
-    <t>569.75M</t>
-  </si>
-  <si>
-    <t>+40.36</t>
-  </si>
-  <si>
-    <t>13.06B</t>
-  </si>
-  <si>
-    <t>+31.75</t>
-  </si>
-  <si>
-    <t>138.94M</t>
-  </si>
-  <si>
-    <t>+22.16</t>
-  </si>
-  <si>
-    <t>30.90B</t>
-  </si>
-  <si>
-    <t>+120.15</t>
-  </si>
-  <si>
-    <t>3.12B</t>
-  </si>
-  <si>
-    <t>+72.11</t>
-  </si>
-  <si>
     <t>3.41</t>
   </si>
   <si>
-    <t>3.64B</t>
-  </si>
-  <si>
-    <t>+71.97</t>
-  </si>
-  <si>
-    <t>25.22B</t>
-  </si>
-  <si>
-    <t>+52.26</t>
-  </si>
-  <si>
     <t>2.97</t>
   </si>
   <si>
     <t>-2.79</t>
   </si>
   <si>
-    <t>16.14B</t>
-  </si>
-  <si>
-    <t>+28.59</t>
-  </si>
-  <si>
     <t>1.85</t>
   </si>
   <si>
-    <t>26.60B</t>
-  </si>
-  <si>
-    <t>+28.10</t>
-  </si>
-  <si>
     <t>2.55</t>
   </si>
   <si>
     <t>-3.89</t>
   </si>
   <si>
-    <t>SI-BONE, Inc.</t>
-  </si>
-  <si>
-    <t>SIBN</t>
-  </si>
-  <si>
-    <t>540.58M</t>
-  </si>
-  <si>
-    <t>+36.50</t>
-  </si>
-  <si>
-    <t>7.29</t>
-  </si>
-  <si>
-    <t>-2.84</t>
-  </si>
-  <si>
-    <t>12.57B</t>
-  </si>
-  <si>
-    <t>+21.79</t>
-  </si>
-  <si>
     <t>4.48</t>
   </si>
   <si>
@@ -815,60 +479,12 @@
     <t>DXCM</t>
   </si>
   <si>
-    <t>23.58B</t>
-  </si>
-  <si>
-    <t>+99.59</t>
-  </si>
-  <si>
     <t>6.12</t>
   </si>
   <si>
     <t>-2.92</t>
   </si>
   <si>
-    <t>7.51B</t>
-  </si>
-  <si>
-    <t>+70.45</t>
-  </si>
-  <si>
-    <t>3.63B</t>
-  </si>
-  <si>
-    <t>+64.12</t>
-  </si>
-  <si>
-    <t>Middle East Pharmaceutical Industries Company</t>
-  </si>
-  <si>
-    <t>4016.SR</t>
-  </si>
-  <si>
-    <t>546.67M</t>
-  </si>
-  <si>
-    <t>+31.02</t>
-  </si>
-  <si>
-    <t>9.74</t>
-  </si>
-  <si>
-    <t>Kyowa Kirin Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4151.T</t>
-  </si>
-  <si>
-    <t>8.00B</t>
-  </si>
-  <si>
-    <t>+26.43</t>
-  </si>
-  <si>
-    <t>5.28</t>
-  </si>
-  <si>
     <t>-2.15</t>
   </si>
   <si>
@@ -881,76 +497,493 @@
     <t>5.78B</t>
   </si>
   <si>
-    <t>+23.55</t>
-  </si>
-  <si>
     <t>9.57</t>
   </si>
   <si>
-    <t>-2.72</t>
-  </si>
-  <si>
-    <t>145.73M</t>
-  </si>
-  <si>
-    <t>+20.14</t>
-  </si>
-  <si>
     <t>HealthStream, Inc.</t>
   </si>
   <si>
     <t>HSTM</t>
   </si>
   <si>
-    <t>624.67M</t>
-  </si>
-  <si>
-    <t>+16.00</t>
-  </si>
-  <si>
-    <t>-2.45</t>
-  </si>
-  <si>
     <t>1.06B</t>
   </si>
   <si>
-    <t>+15.60</t>
-  </si>
-  <si>
-    <t>1.12B</t>
-  </si>
-  <si>
-    <t>+32.04</t>
-  </si>
-  <si>
-    <t>Eisai Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4523.T</t>
-  </si>
-  <si>
-    <t>8.48B</t>
-  </si>
-  <si>
-    <t>+6.88</t>
-  </si>
-  <si>
-    <t>2.85</t>
-  </si>
-  <si>
     <t>Laboratorios Farmaceuticos Rovi, S.A.</t>
   </si>
   <si>
     <t>ROVI.MC</t>
   </si>
   <si>
-    <t>4.77B</t>
-  </si>
-  <si>
-    <t>-10.16</t>
-  </si>
-  <si>
     <t>9.75</t>
+  </si>
+  <si>
+    <t>EssilorLuxottica S.A.</t>
+  </si>
+  <si>
+    <t>EL.PA</t>
+  </si>
+  <si>
+    <t>90.87B</t>
+  </si>
+  <si>
+    <t>+25.30</t>
+  </si>
+  <si>
+    <t>-2.68</t>
+  </si>
+  <si>
+    <t>Steady</t>
+  </si>
+  <si>
+    <t>25.07B</t>
+  </si>
+  <si>
+    <t>+123.78</t>
+  </si>
+  <si>
+    <t>7.88B</t>
+  </si>
+  <si>
+    <t>+62.38</t>
+  </si>
+  <si>
+    <t>46.27M</t>
+  </si>
+  <si>
+    <t>+244.92</t>
+  </si>
+  <si>
+    <t>3.40B</t>
+  </si>
+  <si>
+    <t>+57.98</t>
+  </si>
+  <si>
+    <t>3.51B</t>
+  </si>
+  <si>
+    <t>+57.84</t>
+  </si>
+  <si>
+    <t>-3.51</t>
+  </si>
+  <si>
+    <t>3.56B</t>
+  </si>
+  <si>
+    <t>+75.31</t>
+  </si>
+  <si>
+    <t>812.60M</t>
+  </si>
+  <si>
+    <t>+42.97</t>
+  </si>
+  <si>
+    <t>17.39B</t>
+  </si>
+  <si>
+    <t>+28.49</t>
+  </si>
+  <si>
+    <t>-2.31</t>
+  </si>
+  <si>
+    <t>26.56B</t>
+  </si>
+  <si>
+    <t>+28.27</t>
+  </si>
+  <si>
+    <t>12.26B</t>
+  </si>
+  <si>
+    <t>+27.43</t>
+  </si>
+  <si>
+    <t>40.77B</t>
+  </si>
+  <si>
+    <t>+27.35</t>
+  </si>
+  <si>
+    <t>2.52</t>
+  </si>
+  <si>
+    <t>-4.77</t>
+  </si>
+  <si>
+    <t>629.79M</t>
+  </si>
+  <si>
+    <t>+26.98</t>
+  </si>
+  <si>
+    <t>134.75M</t>
+  </si>
+  <si>
+    <t>+25.96</t>
+  </si>
+  <si>
+    <t>663.60M</t>
+  </si>
+  <si>
+    <t>+15.23</t>
+  </si>
+  <si>
+    <t>3.15</t>
+  </si>
+  <si>
+    <t>48.06B</t>
+  </si>
+  <si>
+    <t>+12.15</t>
+  </si>
+  <si>
+    <t>12.30B</t>
+  </si>
+  <si>
+    <t>+55.78</t>
+  </si>
+  <si>
+    <t>1.52B</t>
+  </si>
+  <si>
+    <t>-5.99</t>
+  </si>
+  <si>
+    <t>50.18B</t>
+  </si>
+  <si>
+    <t>+45.10</t>
+  </si>
+  <si>
+    <t>IQVIA Holdings Inc.</t>
+  </si>
+  <si>
+    <t>IQV</t>
+  </si>
+  <si>
+    <t>27.43B</t>
+  </si>
+  <si>
+    <t>+40.58</t>
+  </si>
+  <si>
+    <t>1.83</t>
+  </si>
+  <si>
+    <t>-2.87</t>
+  </si>
+  <si>
+    <t>12.24B</t>
+  </si>
+  <si>
+    <t>+25.07</t>
+  </si>
+  <si>
+    <t>11.97B</t>
+  </si>
+  <si>
+    <t>+21.03</t>
+  </si>
+  <si>
+    <t>13.62B</t>
+  </si>
+  <si>
+    <t>+14.66</t>
+  </si>
+  <si>
+    <t>13.12B</t>
+  </si>
+  <si>
+    <t>+30.91</t>
+  </si>
+  <si>
+    <t>43.79B</t>
+  </si>
+  <si>
+    <t>+13.17</t>
+  </si>
+  <si>
+    <t>10.97B</t>
+  </si>
+  <si>
+    <t>+29.81</t>
+  </si>
+  <si>
+    <t>3.57</t>
+  </si>
+  <si>
+    <t>-2.55</t>
+  </si>
+  <si>
+    <t>16.23B</t>
+  </si>
+  <si>
+    <t>+27.95</t>
+  </si>
+  <si>
+    <t>10.61B</t>
+  </si>
+  <si>
+    <t>+16.65</t>
+  </si>
+  <si>
+    <t>73.42B</t>
+  </si>
+  <si>
+    <t>+7.49</t>
+  </si>
+  <si>
+    <t>9.55B</t>
+  </si>
+  <si>
+    <t>+56.05</t>
+  </si>
+  <si>
+    <t>M3, Inc.</t>
+  </si>
+  <si>
+    <t>2413.T</t>
+  </si>
+  <si>
+    <t>6.42B</t>
+  </si>
+  <si>
+    <t>+52.96</t>
+  </si>
+  <si>
+    <t>5.37</t>
+  </si>
+  <si>
+    <t>174.48M</t>
+  </si>
+  <si>
+    <t>+0.35</t>
+  </si>
+  <si>
+    <t>1.55B</t>
+  </si>
+  <si>
+    <t>+65.23</t>
+  </si>
+  <si>
+    <t>4.79B</t>
+  </si>
+  <si>
+    <t>-10.95</t>
+  </si>
+  <si>
+    <t>Cochlear Limited</t>
+  </si>
+  <si>
+    <t>COH.AX</t>
+  </si>
+  <si>
+    <t>4.68B</t>
+  </si>
+  <si>
+    <t>+107.70</t>
+  </si>
+  <si>
+    <t>14.11</t>
+  </si>
+  <si>
+    <t>-2.48</t>
+  </si>
+  <si>
+    <t>+23.42</t>
+  </si>
+  <si>
+    <t>-2.33</t>
+  </si>
+  <si>
+    <t>9.88B</t>
+  </si>
+  <si>
+    <t>+7.08</t>
+  </si>
+  <si>
+    <t>Johnson &amp; Johnson</t>
+  </si>
+  <si>
+    <t>JNJ</t>
+  </si>
+  <si>
+    <t>553.26B</t>
+  </si>
+  <si>
+    <t>-4.14</t>
+  </si>
+  <si>
+    <t>5.06</t>
+  </si>
+  <si>
+    <t>-2.52</t>
+  </si>
+  <si>
+    <t>Hologic, Inc.</t>
+  </si>
+  <si>
+    <t>HOLX</t>
+  </si>
+  <si>
+    <t>17.06B</t>
+  </si>
+  <si>
+    <t>-4.96</t>
+  </si>
+  <si>
+    <t>4.18</t>
+  </si>
+  <si>
+    <t>165.23B</t>
+  </si>
+  <si>
+    <t>+119.36</t>
+  </si>
+  <si>
+    <t>103.90B</t>
+  </si>
+  <si>
+    <t>+77.69</t>
+  </si>
+  <si>
+    <t>Laboratory Corporation of America Holdings</t>
+  </si>
+  <si>
+    <t>LH</t>
+  </si>
+  <si>
+    <t>20.96B</t>
+  </si>
+  <si>
+    <t>+25.58</t>
+  </si>
+  <si>
+    <t>3.05</t>
+  </si>
+  <si>
+    <t>-2.47</t>
+  </si>
+  <si>
+    <t>West Pharmaceutical Services, Inc.</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>21.92B</t>
+  </si>
+  <si>
+    <t>+3.77</t>
+  </si>
+  <si>
+    <t>12.85</t>
+  </si>
+  <si>
+    <t>-3.59</t>
+  </si>
+  <si>
+    <t>HOYA Corporation</t>
+  </si>
+  <si>
+    <t>7741.T</t>
+  </si>
+  <si>
+    <t>60.04B</t>
+  </si>
+  <si>
+    <t>-0.64</t>
+  </si>
+  <si>
+    <t>23.49</t>
+  </si>
+  <si>
+    <t>-2.66</t>
+  </si>
+  <si>
+    <t>23.01B</t>
+  </si>
+  <si>
+    <t>+104.54</t>
+  </si>
+  <si>
+    <t>U.S. Physical Therapy, Inc.</t>
+  </si>
+  <si>
+    <t>USPH</t>
+  </si>
+  <si>
+    <t>+75.54</t>
+  </si>
+  <si>
+    <t>2.68</t>
+  </si>
+  <si>
+    <t>Definitive Healthcare Corp.</t>
+  </si>
+  <si>
+    <t>DH</t>
+  </si>
+  <si>
+    <t>103.28M</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>-2.18</t>
+  </si>
+  <si>
+    <t>Evolent Health, Inc.</t>
+  </si>
+  <si>
+    <t>EVH</t>
+  </si>
+  <si>
+    <t>442.56M</t>
+  </si>
+  <si>
+    <t>+165.03</t>
+  </si>
+  <si>
+    <t>-0.43</t>
+  </si>
+  <si>
+    <t>-5.68</t>
+  </si>
+  <si>
+    <t>Progyny, Inc.</t>
+  </si>
+  <si>
+    <t>PGNY</t>
+  </si>
+  <si>
+    <t>1.62B</t>
+  </si>
+  <si>
+    <t>+72.24</t>
+  </si>
+  <si>
+    <t>8.48</t>
+  </si>
+  <si>
+    <t>1.08B</t>
+  </si>
+  <si>
+    <t>+55.22</t>
+  </si>
+  <si>
+    <t>1.40B</t>
+  </si>
+  <si>
+    <t>+68.84</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8295A055-0859-4227-AD35-9F88769F91FB}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -1367,68 +1400,68 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="F2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>164</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
@@ -1436,36 +1469,36 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G6" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
@@ -1473,36 +1506,36 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="F8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
@@ -1510,36 +1543,36 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="F10" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>181</v>
+        <v>102</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
@@ -1547,36 +1580,36 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G12" t="s">
-        <v>186</v>
+        <v>92</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -1584,73 +1617,73 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>183</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="G16" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
@@ -1658,36 +1691,36 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="G18" t="s">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="I18" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
@@ -1695,36 +1728,36 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="G20" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H20" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I20" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
@@ -1732,36 +1765,36 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="E22" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="G22" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I22" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
@@ -1769,36 +1802,36 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E24" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="F24" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G24" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="I24" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
@@ -1806,36 +1839,36 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="F26" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
@@ -1843,36 +1876,36 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>195</v>
+      </c>
+      <c r="G28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" t="s">
         <v>14</v>
       </c>
-      <c r="B28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C28" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" t="s">
-        <v>130</v>
-      </c>
-      <c r="F28" t="s">
-        <v>199</v>
-      </c>
-      <c r="G28" t="s">
-        <v>132</v>
-      </c>
-      <c r="H28" t="s">
-        <v>30</v>
-      </c>
       <c r="I28" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
@@ -1880,36 +1913,36 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="C30" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="D30" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="F30" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G30" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H30" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I30" t="s">
-        <v>205</v>
+        <v>96</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -1917,36 +1950,36 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>201</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F32" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I32" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
@@ -1954,73 +1987,73 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>208</v>
+        <v>66</v>
       </c>
       <c r="D34" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="E34" t="s">
-        <v>208</v>
+        <v>66</v>
       </c>
       <c r="F34" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="G34" t="s">
-        <v>212</v>
+        <v>68</v>
       </c>
       <c r="H34" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="I34" t="s">
-        <v>213</v>
+        <v>36</v>
       </c>
       <c r="J34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>209</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>214</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>214</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="E36" t="s">
-        <v>214</v>
+        <v>99</v>
       </c>
       <c r="F36" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="G36" t="s">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="H36" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="I36" t="s">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
@@ -2028,36 +2061,36 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>215</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="E38" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="F38" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="G38" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H38" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="I38" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="J38" t="s">
         <v>15</v>
@@ -2065,36 +2098,36 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="D40" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="F40" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="G40" t="s">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="H40" t="s">
         <v>19</v>
       </c>
       <c r="I40" t="s">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="J40" t="s">
         <v>15</v>
@@ -2102,36 +2135,36 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>17</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="D42" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="F42" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G42" t="s">
-        <v>23</v>
+        <v>144</v>
       </c>
       <c r="H42" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="J42" t="s">
         <v>15</v>
@@ -2139,36 +2172,36 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F44" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H44" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="I44" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J44" t="s">
         <v>15</v>
@@ -2176,36 +2209,36 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D46" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E46" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F46" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="G46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H46" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I46" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J46" t="s">
         <v>15</v>
@@ -2213,36 +2246,36 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="D48" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="E48" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="G48" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I48" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s">
         <v>15</v>
@@ -2250,36 +2283,36 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D50" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E50" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="F50" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="G50" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I50" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="J50" t="s">
         <v>15</v>
@@ -2287,36 +2320,36 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E52" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="F52" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="G52" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="H52" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>133</v>
+        <v>226</v>
       </c>
       <c r="J52" t="s">
         <v>15</v>
@@ -2324,36 +2357,36 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D54" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E54" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F54" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G54" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I54" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J54" t="s">
         <v>15</v>
@@ -2361,36 +2394,36 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
+        <v>27</v>
+      </c>
+      <c r="B56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C56" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" t="s">
+        <v>229</v>
+      </c>
+      <c r="E56" t="s">
+        <v>50</v>
+      </c>
+      <c r="F56" t="s">
+        <v>230</v>
+      </c>
+      <c r="G56" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" t="s">
         <v>28</v>
       </c>
-      <c r="B56" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" t="s">
-        <v>62</v>
-      </c>
-      <c r="D56" t="s">
-        <v>237</v>
-      </c>
-      <c r="E56" t="s">
-        <v>62</v>
-      </c>
-      <c r="F56" t="s">
-        <v>238</v>
-      </c>
-      <c r="G56" t="s">
-        <v>239</v>
-      </c>
-      <c r="H56" t="s">
-        <v>30</v>
-      </c>
       <c r="I56" t="s">
-        <v>240</v>
+        <v>121</v>
       </c>
       <c r="J56" t="s">
         <v>15</v>
@@ -2398,36 +2431,36 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B58" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="D58" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E58" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="F58" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="G58" t="s">
-        <v>243</v>
+        <v>119</v>
       </c>
       <c r="H58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I58" t="s">
-        <v>148</v>
+        <v>71</v>
       </c>
       <c r="J58" t="s">
         <v>15</v>
@@ -2435,36 +2468,36 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="D60" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E60" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="F60" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="G60" t="s">
-        <v>246</v>
+        <v>41</v>
       </c>
       <c r="H60" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I60" t="s">
-        <v>247</v>
+        <v>42</v>
       </c>
       <c r="J60" t="s">
         <v>15</v>
@@ -2472,73 +2505,73 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="C62" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D62" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E62" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="F62" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="G62" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="H62" t="s">
         <v>14</v>
       </c>
       <c r="I62" t="s">
-        <v>253</v>
+        <v>129</v>
       </c>
       <c r="J62" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="D64" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E64" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="F64" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="G64" t="s">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c r="H64" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I64" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="J64" t="s">
         <v>15</v>
@@ -2546,36 +2579,36 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="C66" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
       <c r="E66" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>243</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="H66" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I66" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="J66" t="s">
         <v>15</v>
@@ -2583,73 +2616,73 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="D68" t="s">
-        <v>149</v>
+        <v>244</v>
       </c>
       <c r="E68" t="s">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="F68" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="G68" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="H68" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I68" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J68" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>9</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B70" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C70" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D70" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E70" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F70" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="G70" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="H70" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="I70" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="J70" t="s">
         <v>13</v>
@@ -2657,36 +2690,36 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="C72" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>263</v>
+        <v>152</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="F72" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="G72" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="H72" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I72" t="s">
-        <v>26</v>
+        <v>253</v>
       </c>
       <c r="J72" t="s">
         <v>15</v>
@@ -2694,36 +2727,36 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B74" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D74" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="E74" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="F74" t="s">
-        <v>154</v>
+        <v>255</v>
       </c>
       <c r="G74" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="H74" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I74" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="J74" t="s">
         <v>15</v>
@@ -2731,73 +2764,73 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>256</v>
       </c>
       <c r="C76" t="s">
-        <v>71</v>
+        <v>256</v>
       </c>
       <c r="D76" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E76" t="s">
-        <v>71</v>
+        <v>256</v>
       </c>
       <c r="F76" t="s">
-        <v>168</v>
+        <v>259</v>
       </c>
       <c r="G76" t="s">
-        <v>73</v>
+        <v>260</v>
       </c>
       <c r="H76" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="I76" t="s">
-        <v>74</v>
+        <v>261</v>
       </c>
       <c r="J76" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>72</v>
+        <v>257</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>262</v>
       </c>
       <c r="C78" t="s">
-        <v>93</v>
+        <v>262</v>
       </c>
       <c r="D78" t="s">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="E78" t="s">
-        <v>93</v>
+        <v>262</v>
       </c>
       <c r="F78" t="s">
-        <v>166</v>
+        <v>265</v>
       </c>
       <c r="G78" t="s">
-        <v>96</v>
+        <v>266</v>
       </c>
       <c r="H78" t="s">
         <v>14</v>
       </c>
       <c r="I78" t="s">
-        <v>125</v>
+        <v>251</v>
       </c>
       <c r="J78" t="s">
         <v>15</v>
@@ -2805,73 +2838,73 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>94</v>
+        <v>263</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B80" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="D80" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E80" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G80" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="H80" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I80" t="s">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="J80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="E82" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F82" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="G82" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="H82" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I82" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="J82" t="s">
         <v>15</v>
@@ -2879,73 +2912,73 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C84" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D84" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E84" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F84" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G84" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H84" t="s">
         <v>14</v>
       </c>
       <c r="I84" t="s">
-        <v>118</v>
+        <v>276</v>
       </c>
       <c r="J84" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B86" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C86" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D86" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E86" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F86" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G86" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H86" t="s">
         <v>14</v>
       </c>
       <c r="I86" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J86" t="s">
         <v>15</v>
@@ -2953,36 +2986,36 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B88" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C88" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D88" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E88" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F88" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G88" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H88" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I88" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J88" t="s">
         <v>15</v>
@@ -2990,110 +3023,110 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="C90" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="D90" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E90" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="F90" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G90" t="s">
-        <v>261</v>
+        <v>147</v>
       </c>
       <c r="H90" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I90" t="s">
-        <v>277</v>
+        <v>148</v>
       </c>
       <c r="J90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>33</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C92" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D92" t="s">
-        <v>288</v>
+        <v>156</v>
       </c>
       <c r="E92" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F92" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G92" t="s">
-        <v>147</v>
+        <v>294</v>
       </c>
       <c r="H92" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>290</v>
+        <v>38</v>
       </c>
       <c r="J92" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B94" t="s">
-        <v>27</v>
+        <v>295</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>295</v>
       </c>
       <c r="D94" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E94" t="s">
-        <v>27</v>
+        <v>295</v>
       </c>
       <c r="F94" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G94" t="s">
-        <v>29</v>
+        <v>299</v>
       </c>
       <c r="H94" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I94" t="s">
-        <v>31</v>
+        <v>300</v>
       </c>
       <c r="J94" t="s">
         <v>15</v>
@@ -3101,36 +3134,36 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>28</v>
+        <v>296</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B96" t="s">
-        <v>87</v>
+        <v>301</v>
       </c>
       <c r="C96" t="s">
-        <v>87</v>
+        <v>301</v>
       </c>
       <c r="D96" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E96" t="s">
-        <v>87</v>
+        <v>301</v>
       </c>
       <c r="F96" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="G96" t="s">
-        <v>89</v>
+        <v>305</v>
       </c>
       <c r="H96" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I96" t="s">
-        <v>90</v>
+        <v>306</v>
       </c>
       <c r="J96" t="s">
         <v>13</v>
@@ -3138,73 +3171,73 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>88</v>
+        <v>302</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B98" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C98" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D98" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E98" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="F98" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="G98" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="H98" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I98" t="s">
-        <v>12</v>
+        <v>212</v>
       </c>
       <c r="J98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B100" t="s">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="C100" t="s">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="D100" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="E100" t="s">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="F100" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="G100" t="s">
-        <v>304</v>
+        <v>132</v>
       </c>
       <c r="H100" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="I100" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="J100" t="s">
         <v>15</v>
@@ -3212,7 +3245,44 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>301</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>50</v>
+      </c>
+      <c r="B102" t="s">
+        <v>134</v>
+      </c>
+      <c r="C102" t="s">
+        <v>134</v>
+      </c>
+      <c r="D102" t="s">
+        <v>314</v>
+      </c>
+      <c r="E102" t="s">
+        <v>134</v>
+      </c>
+      <c r="F102" t="s">
+        <v>315</v>
+      </c>
+      <c r="G102" t="s">
+        <v>136</v>
+      </c>
+      <c r="H102" t="s">
+        <v>65</v>
+      </c>
+      <c r="I102" t="s">
+        <v>137</v>
+      </c>
+      <c r="J102" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0FA30BB-2EF1-47C6-AD43-60E2FEB7BD2F}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57867E9F-4360-4EB5-9095-EBD2BE8AC3B2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5AC1432C-0454-491C-B311-8CBC9194BD16}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="311">
   <si>
     <t>Symbol</t>
   </si>
@@ -80,12 +80,6 @@
     <t>Robust</t>
   </si>
   <si>
-    <t>AMN Healthcare Services, Inc.</t>
-  </si>
-  <si>
-    <t>AMN</t>
-  </si>
-  <si>
     <t>5.0</t>
   </si>
   <si>
@@ -167,9 +161,6 @@
     <t>EXEL</t>
   </si>
   <si>
-    <t>-3.50</t>
-  </si>
-  <si>
     <t>Innoviva, Inc.</t>
   </si>
   <si>
@@ -245,12 +236,6 @@
     <t>CNC</t>
   </si>
   <si>
-    <t>Sanofi</t>
-  </si>
-  <si>
-    <t>SAN.PA</t>
-  </si>
-  <si>
     <t>Medpace Holdings, Inc.</t>
   </si>
   <si>
@@ -266,12 +251,6 @@
     <t>OPCH</t>
   </si>
   <si>
-    <t>1.93</t>
-  </si>
-  <si>
-    <t>-1.64</t>
-  </si>
-  <si>
     <t>Regeneron Pharmaceuticals, Inc.</t>
   </si>
   <si>
@@ -341,30 +320,12 @@
     <t>4.48</t>
   </si>
   <si>
-    <t>Chemed Corporation</t>
-  </si>
-  <si>
-    <t>CHE</t>
-  </si>
-  <si>
-    <t>5.78B</t>
-  </si>
-  <si>
-    <t>9.57</t>
-  </si>
-  <si>
     <t>HealthStream, Inc.</t>
   </si>
   <si>
     <t>HSTM</t>
   </si>
   <si>
-    <t>Laboratorios Farmaceuticos Rovi, S.A.</t>
-  </si>
-  <si>
-    <t>ROVI.MC</t>
-  </si>
-  <si>
     <t>EssilorLuxottica S.A.</t>
   </si>
   <si>
@@ -377,15 +338,9 @@
     <t>Steady</t>
   </si>
   <si>
-    <t>3.51B</t>
-  </si>
-  <si>
     <t>-3.51</t>
   </si>
   <si>
-    <t>+28.27</t>
-  </si>
-  <si>
     <t>2.52</t>
   </si>
   <si>
@@ -395,18 +350,6 @@
     <t>3.15</t>
   </si>
   <si>
-    <t>IQVIA Holdings Inc.</t>
-  </si>
-  <si>
-    <t>IQV</t>
-  </si>
-  <si>
-    <t>1.83</t>
-  </si>
-  <si>
-    <t>-2.87</t>
-  </si>
-  <si>
     <t>M3, Inc.</t>
   </si>
   <si>
@@ -419,9 +362,6 @@
     <t>-2.48</t>
   </si>
   <si>
-    <t>-2.33</t>
-  </si>
-  <si>
     <t>West Pharmaceutical Services, Inc.</t>
   </si>
   <si>
@@ -434,18 +374,6 @@
     <t>-3.59</t>
   </si>
   <si>
-    <t>HOYA Corporation</t>
-  </si>
-  <si>
-    <t>7741.T</t>
-  </si>
-  <si>
-    <t>23.49</t>
-  </si>
-  <si>
-    <t>-2.66</t>
-  </si>
-  <si>
     <t>--</t>
   </si>
   <si>
@@ -464,60 +392,24 @@
     <t>QIA.DE</t>
   </si>
   <si>
-    <t>6.85B</t>
-  </si>
-  <si>
-    <t>+125.68</t>
-  </si>
-  <si>
     <t>3.59</t>
   </si>
   <si>
     <t>-2.61</t>
   </si>
   <si>
-    <t>7.93B</t>
-  </si>
-  <si>
-    <t>+63.11</t>
-  </si>
-  <si>
     <t>-2.75</t>
   </si>
   <si>
-    <t>9.32B</t>
-  </si>
-  <si>
-    <t>+37.40</t>
-  </si>
-  <si>
     <t>9.71</t>
   </si>
   <si>
-    <t>42.57M</t>
-  </si>
-  <si>
-    <t>+274.88</t>
-  </si>
-  <si>
-    <t>1.63B</t>
-  </si>
-  <si>
-    <t>+140.37</t>
-  </si>
-  <si>
     <t>3.86</t>
   </si>
   <si>
     <t>-3.33</t>
   </si>
   <si>
-    <t>438.88M</t>
-  </si>
-  <si>
-    <t>+87.98</t>
-  </si>
-  <si>
     <t>3.33</t>
   </si>
   <si>
@@ -527,48 +419,24 @@
     <t>-3.99</t>
   </si>
   <si>
-    <t>3.06B</t>
-  </si>
-  <si>
-    <t>+75.46</t>
-  </si>
-  <si>
-    <t>+68.93</t>
-  </si>
-  <si>
     <t>Prestige Consumer Healthcare Inc.</t>
   </si>
   <si>
     <t>PBH</t>
   </si>
   <si>
-    <t>2.27B</t>
-  </si>
-  <si>
-    <t>+66.76</t>
-  </si>
-  <si>
     <t>2.48</t>
   </si>
   <si>
     <t>3.44B</t>
   </si>
   <si>
-    <t>+60.88</t>
-  </si>
-  <si>
     <t>Fresenius Medical Care AG &amp; Co. KGaA</t>
   </si>
   <si>
     <t>FME.DE</t>
   </si>
   <si>
-    <t>11.91B</t>
-  </si>
-  <si>
-    <t>+56.99</t>
-  </si>
-  <si>
     <t>1.31</t>
   </si>
   <si>
@@ -581,12 +449,6 @@
     <t>GRF.MC</t>
   </si>
   <si>
-    <t>7.19B</t>
-  </si>
-  <si>
-    <t>+105.39</t>
-  </si>
-  <si>
     <t>1.06</t>
   </si>
   <si>
@@ -599,12 +461,6 @@
     <t>4014.SR</t>
   </si>
   <si>
-    <t>238.83M</t>
-  </si>
-  <si>
-    <t>+48.02</t>
-  </si>
-  <si>
     <t>3.22</t>
   </si>
   <si>
@@ -614,12 +470,6 @@
     <t>4151.T</t>
   </si>
   <si>
-    <t>7.81B</t>
-  </si>
-  <si>
-    <t>+32.26</t>
-  </si>
-  <si>
     <t>6.34</t>
   </si>
   <si>
@@ -632,12 +482,6 @@
     <t>HAE</t>
   </si>
   <si>
-    <t>2.66B</t>
-  </si>
-  <si>
-    <t>+29.24</t>
-  </si>
-  <si>
     <t>2.08</t>
   </si>
   <si>
@@ -647,12 +491,6 @@
     <t>REC.MI</t>
   </si>
   <si>
-    <t>12.22B</t>
-  </si>
-  <si>
-    <t>+24.85</t>
-  </si>
-  <si>
     <t>3.53</t>
   </si>
   <si>
@@ -665,316 +503,472 @@
     <t>COLL</t>
   </si>
   <si>
-    <t>+22.29</t>
-  </si>
-  <si>
     <t>1.48</t>
   </si>
   <si>
     <t>-2.60</t>
   </si>
   <si>
-    <t>160.94B</t>
-  </si>
-  <si>
-    <t>+127.50</t>
-  </si>
-  <si>
     <t>37.46</t>
   </si>
   <si>
-    <t>92.45B</t>
-  </si>
-  <si>
-    <t>+22.37</t>
-  </si>
-  <si>
-    <t>31.33B</t>
-  </si>
-  <si>
-    <t>+121.80</t>
-  </si>
-  <si>
     <t>5.58</t>
   </si>
   <si>
-    <t>26.22B</t>
-  </si>
-  <si>
-    <t>+112.47</t>
-  </si>
-  <si>
-    <t>12.95B</t>
-  </si>
-  <si>
-    <t>+22.70</t>
-  </si>
-  <si>
     <t>12.74</t>
   </si>
   <si>
     <t>-3.55</t>
   </si>
   <si>
-    <t>11.81B</t>
-  </si>
-  <si>
-    <t>+22.61</t>
-  </si>
-  <si>
-    <t>5.94B</t>
-  </si>
-  <si>
-    <t>+20.10</t>
-  </si>
-  <si>
-    <t>12.84B</t>
-  </si>
-  <si>
-    <t>+19.41</t>
-  </si>
-  <si>
-    <t>11.23B</t>
-  </si>
-  <si>
-    <t>+36.32</t>
-  </si>
-  <si>
-    <t>+17.93</t>
-  </si>
-  <si>
-    <t>13.14</t>
-  </si>
-  <si>
-    <t>-2.51</t>
-  </si>
-  <si>
     <t>Daiichi Sankyo Company, Limited</t>
   </si>
   <si>
     <t>4568.T</t>
   </si>
   <si>
-    <t>29.99B</t>
-  </si>
-  <si>
-    <t>+59.70</t>
-  </si>
-  <si>
     <t>2.93</t>
   </si>
   <si>
     <t>-2.08</t>
   </si>
   <si>
-    <t>39.74B</t>
-  </si>
-  <si>
-    <t>28.67B</t>
-  </si>
-  <si>
-    <t>+18.83</t>
-  </si>
-  <si>
     <t>Theravance Biopharma, Inc.</t>
   </si>
   <si>
     <t>TBPH</t>
   </si>
   <si>
-    <t>831.75M</t>
-  </si>
-  <si>
-    <t>+13.26</t>
-  </si>
-  <si>
     <t>2.21</t>
   </si>
   <si>
     <t>-4.59</t>
   </si>
   <si>
-    <t>764.58M</t>
-  </si>
-  <si>
-    <t>+97.21</t>
-  </si>
-  <si>
     <t>2.19</t>
   </si>
   <si>
-    <t>1.43B</t>
-  </si>
-  <si>
-    <t>+68.12</t>
-  </si>
-  <si>
     <t>2.18</t>
   </si>
   <si>
     <t>-2.86</t>
   </si>
   <si>
-    <t>1.88B</t>
-  </si>
-  <si>
-    <t>+57.16</t>
-  </si>
-  <si>
     <t>5.95</t>
   </si>
   <si>
-    <t>28.48B</t>
-  </si>
-  <si>
-    <t>+35.39</t>
-  </si>
-  <si>
-    <t>41.85B</t>
-  </si>
-  <si>
-    <t>+17.70</t>
-  </si>
-  <si>
-    <t>144.76M</t>
-  </si>
-  <si>
-    <t>+17.63</t>
-  </si>
-  <si>
     <t>Lumexa Imaging Holdings, Inc. Common Stock</t>
   </si>
   <si>
     <t>LMRI</t>
   </si>
   <si>
-    <t>674.76M</t>
-  </si>
-  <si>
-    <t>+15.50</t>
-  </si>
-  <si>
     <t>0.83</t>
   </si>
   <si>
-    <t>10.72B</t>
-  </si>
-  <si>
-    <t>+15.45</t>
-  </si>
-  <si>
-    <t>666.84M</t>
-  </si>
-  <si>
-    <t>+14.67</t>
-  </si>
-  <si>
-    <t>9.42B</t>
-  </si>
-  <si>
-    <t>+12.19</t>
-  </si>
-  <si>
     <t>IDEXX Laboratories, Inc.</t>
   </si>
   <si>
     <t>IDXX</t>
   </si>
   <si>
-    <t>42.35B</t>
-  </si>
-  <si>
-    <t>+10.27</t>
-  </si>
-  <si>
     <t>2.74</t>
   </si>
   <si>
-    <t>72.62B</t>
-  </si>
-  <si>
-    <t>+8.68</t>
-  </si>
-  <si>
     <t>Electromed, Inc.</t>
   </si>
   <si>
     <t>ELMD</t>
   </si>
   <si>
-    <t>292.98M</t>
-  </si>
-  <si>
-    <t>-2.02</t>
-  </si>
-  <si>
     <t>14.47</t>
   </si>
   <si>
     <t>1.48B</t>
   </si>
   <si>
-    <t>-4.00</t>
-  </si>
-  <si>
-    <t>103.54B</t>
-  </si>
-  <si>
-    <t>+77.16</t>
-  </si>
-  <si>
-    <t>21.81B</t>
-  </si>
-  <si>
-    <t>+4.30</t>
-  </si>
-  <si>
-    <t>59.99B</t>
-  </si>
-  <si>
-    <t>-1.26</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Limited</t>
-  </si>
-  <si>
-    <t>SUNPHARMA.NS</t>
-  </si>
-  <si>
-    <t>46.93B</t>
-  </si>
-  <si>
-    <t>+37.65</t>
-  </si>
-  <si>
-    <t>15.35</t>
-  </si>
-  <si>
-    <t>-3.54</t>
-  </si>
-  <si>
-    <t>1.11B</t>
-  </si>
-  <si>
-    <t>-42.12</t>
-  </si>
-  <si>
-    <t>1.59</t>
-  </si>
-  <si>
-    <t>Select Medical Holdings Corporation</t>
-  </si>
-  <si>
-    <t>SEM</t>
-  </si>
-  <si>
-    <t>2.04B</t>
-  </si>
-  <si>
-    <t>1.14</t>
-  </si>
-  <si>
-    <t>-2.35</t>
+    <t>7.15B</t>
+  </si>
+  <si>
+    <t>+115.75</t>
+  </si>
+  <si>
+    <t>43.40M</t>
+  </si>
+  <si>
+    <t>+267.74</t>
+  </si>
+  <si>
+    <t>1.62B</t>
+  </si>
+  <si>
+    <t>+141.96</t>
+  </si>
+  <si>
+    <t>458.83M</t>
+  </si>
+  <si>
+    <t>+79.80</t>
+  </si>
+  <si>
+    <t>2.23B</t>
+  </si>
+  <si>
+    <t>+69.22</t>
+  </si>
+  <si>
+    <t>234.47M</t>
+  </si>
+  <si>
+    <t>+51.01</t>
+  </si>
+  <si>
+    <t>2.00B</t>
+  </si>
+  <si>
+    <t>+48.18</t>
+  </si>
+  <si>
+    <t>3.25B</t>
+  </si>
+  <si>
+    <t>+65.06</t>
+  </si>
+  <si>
+    <t>+61.25</t>
+  </si>
+  <si>
+    <t>6.06B</t>
+  </si>
+  <si>
+    <t>+61.03</t>
+  </si>
+  <si>
+    <t>8.14B</t>
+  </si>
+  <si>
+    <t>+58.90</t>
+  </si>
+  <si>
+    <t>9.34B</t>
+  </si>
+  <si>
+    <t>+37.08</t>
+  </si>
+  <si>
+    <t>+22.26</t>
+  </si>
+  <si>
+    <t>12.25B</t>
+  </si>
+  <si>
+    <t>+52.40</t>
+  </si>
+  <si>
+    <t>835.19M</t>
+  </si>
+  <si>
+    <t>+12.79</t>
+  </si>
+  <si>
+    <t>793.59M</t>
+  </si>
+  <si>
+    <t>+90.01</t>
+  </si>
+  <si>
+    <t>7.22B</t>
+  </si>
+  <si>
+    <t>+104.27</t>
+  </si>
+  <si>
+    <t>1.40B</t>
+  </si>
+  <si>
+    <t>+71.86</t>
+  </si>
+  <si>
+    <t>WuXi Biologics (Cayman) Inc.</t>
+  </si>
+  <si>
+    <t>2269.HK</t>
+  </si>
+  <si>
+    <t>16.97B</t>
+  </si>
+  <si>
+    <t>+31.76</t>
+  </si>
+  <si>
+    <t>8.13</t>
+  </si>
+  <si>
+    <t>-2.31</t>
+  </si>
+  <si>
+    <t>7.85B</t>
+  </si>
+  <si>
+    <t>+31.54</t>
+  </si>
+  <si>
+    <t>12.07B</t>
+  </si>
+  <si>
+    <t>+26.20</t>
+  </si>
+  <si>
+    <t>676.23M</t>
+  </si>
+  <si>
+    <t>+15.25</t>
+  </si>
+  <si>
+    <t>163.61B</t>
+  </si>
+  <si>
+    <t>+123.79</t>
+  </si>
+  <si>
+    <t>93.76B</t>
+  </si>
+  <si>
+    <t>+20.45</t>
+  </si>
+  <si>
+    <t>26.13B</t>
+  </si>
+  <si>
+    <t>+113.15</t>
+  </si>
+  <si>
+    <t>32.94B</t>
+  </si>
+  <si>
+    <t>+110.94</t>
+  </si>
+  <si>
+    <t>2.72B</t>
+  </si>
+  <si>
+    <t>+26.00</t>
+  </si>
+  <si>
+    <t>12.80B</t>
+  </si>
+  <si>
+    <t>+24.14</t>
+  </si>
+  <si>
+    <t>11.94B</t>
+  </si>
+  <si>
+    <t>+21.32</t>
+  </si>
+  <si>
+    <t>30.71B</t>
+  </si>
+  <si>
+    <t>+55.94</t>
+  </si>
+  <si>
+    <t>41.10B</t>
+  </si>
+  <si>
+    <t>+24.74</t>
+  </si>
+  <si>
+    <t>66.19B</t>
+  </si>
+  <si>
+    <t>+19.23</t>
+  </si>
+  <si>
+    <t>10.56B</t>
+  </si>
+  <si>
+    <t>+17.19</t>
+  </si>
+  <si>
+    <t>13.44B</t>
+  </si>
+  <si>
+    <t>+14.76</t>
+  </si>
+  <si>
+    <t>11.06B</t>
+  </si>
+  <si>
+    <t>+38.44</t>
+  </si>
+  <si>
+    <t>29.08B</t>
+  </si>
+  <si>
+    <t>+17.18</t>
+  </si>
+  <si>
+    <t>148.67M</t>
+  </si>
+  <si>
+    <t>+14.53</t>
+  </si>
+  <si>
+    <t>43.42B</t>
+  </si>
+  <si>
+    <t>+13.22</t>
+  </si>
+  <si>
+    <t>9.49B</t>
+  </si>
+  <si>
+    <t>+11.31</t>
+  </si>
+  <si>
+    <t>714.13M</t>
+  </si>
+  <si>
+    <t>+7.08</t>
+  </si>
+  <si>
+    <t>21.89B</t>
+  </si>
+  <si>
+    <t>+3.92</t>
+  </si>
+  <si>
+    <t>-3.92</t>
+  </si>
+  <si>
+    <t>314.98M</t>
+  </si>
+  <si>
+    <t>-8.86</t>
+  </si>
+  <si>
+    <t>Definitive Healthcare Corp.</t>
+  </si>
+  <si>
+    <t>DH</t>
+  </si>
+  <si>
+    <t>91.32M</t>
+  </si>
+  <si>
+    <t>-0.60</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Middle East Pharmaceutical Industries Company</t>
+  </si>
+  <si>
+    <t>4016.SR</t>
+  </si>
+  <si>
+    <t>303.34M</t>
+  </si>
+  <si>
+    <t>+165.19</t>
+  </si>
+  <si>
+    <t>9.74</t>
+  </si>
+  <si>
+    <t>-3.44</t>
+  </si>
+  <si>
+    <t>Globus Medical, Inc.</t>
+  </si>
+  <si>
+    <t>GMED</t>
+  </si>
+  <si>
+    <t>10.78B</t>
+  </si>
+  <si>
+    <t>+89.94</t>
+  </si>
+  <si>
+    <t>11.56</t>
+  </si>
+  <si>
+    <t>Mettler-Toledo International Inc.</t>
+  </si>
+  <si>
+    <t>MTD</t>
+  </si>
+  <si>
+    <t>21.61B</t>
+  </si>
+  <si>
+    <t>+38.68</t>
+  </si>
+  <si>
+    <t>6.35</t>
+  </si>
+  <si>
+    <t>Niagen Bioscience Inc</t>
+  </si>
+  <si>
+    <t>NAGE</t>
+  </si>
+  <si>
+    <t>297.29M</t>
+  </si>
+  <si>
+    <t>+95.70</t>
+  </si>
+  <si>
+    <t>6.99</t>
+  </si>
+  <si>
+    <t>-1.53</t>
+  </si>
+  <si>
+    <t>STERIS plc</t>
+  </si>
+  <si>
+    <t>STE</t>
+  </si>
+  <si>
+    <t>21.03B</t>
+  </si>
+  <si>
+    <t>+84.15</t>
+  </si>
+  <si>
+    <t>4.71</t>
+  </si>
+  <si>
+    <t>-2.53</t>
+  </si>
+  <si>
+    <t>DexCom, Inc.</t>
+  </si>
+  <si>
+    <t>DXCM</t>
+  </si>
+  <si>
+    <t>25.57B</t>
+  </si>
+  <si>
+    <t>+84.08</t>
+  </si>
+  <si>
+    <t>6.12</t>
+  </si>
+  <si>
+    <t>-2.92</t>
+  </si>
+  <si>
+    <t>43.97B</t>
+  </si>
+  <si>
+    <t>+6.22</t>
   </si>
 </sst>
 </file>
@@ -1393,25 +1387,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -1419,7 +1413,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1427,25 +1421,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
@@ -1453,7 +1447,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1461,25 +1455,25 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="F6" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="I6" t="s">
         <v>13</v>
@@ -1487,7 +1481,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1495,25 +1489,25 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="I8" t="s">
         <v>13</v>
@@ -1521,7 +1515,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1529,25 +1523,25 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="F10" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="I10" t="s">
         <v>13</v>
@@ -1555,7 +1549,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1563,25 +1557,25 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="E12" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="F12" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="G12" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="I12" t="s">
         <v>13</v>
@@ -1589,7 +1583,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1597,25 +1591,25 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F14" t="s">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="I14" t="s">
         <v>13</v>
@@ -1623,7 +1617,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1631,25 +1625,25 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>197</v>
       </c>
       <c r="E16" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="F16" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
         <v>13</v>
@@ -1657,7 +1651,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1665,25 +1659,25 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>166</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="F18" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="I18" t="s">
         <v>13</v>
@@ -1691,7 +1685,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>167</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1699,25 +1693,25 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="E20" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H20" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s">
         <v>13</v>
@@ -1725,7 +1719,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1733,25 +1727,25 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H22" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="I22" t="s">
         <v>13</v>
@@ -1759,7 +1753,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1767,25 +1761,25 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="E24" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="F24" t="s">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H24" t="s">
-        <v>184</v>
+        <v>119</v>
       </c>
       <c r="I24" t="s">
         <v>13</v>
@@ -1793,7 +1787,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>180</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1801,25 +1795,25 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="D26" t="s">
-        <v>187</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="F26" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="I26" t="s">
         <v>13</v>
@@ -1827,7 +1821,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1835,25 +1829,25 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="E28" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F28" t="s">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H28" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="I28" t="s">
         <v>13</v>
@@ -1861,7 +1855,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>191</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1869,25 +1863,25 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F30" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="G30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>168</v>
       </c>
       <c r="I30" t="s">
         <v>13</v>
@@ -1895,7 +1889,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1903,25 +1897,25 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E32" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="F32" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="G32" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H32" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="I32" t="s">
         <v>13</v>
@@ -1929,7 +1923,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>202</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1937,25 +1931,25 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="C34" t="s">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
       <c r="E34" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F34" t="s">
-        <v>210</v>
+        <v>137</v>
       </c>
       <c r="G34" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>211</v>
+        <v>138</v>
       </c>
       <c r="I34" t="s">
         <v>13</v>
@@ -1963,7 +1957,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>208</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1971,25 +1965,25 @@
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E36" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F36" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="G36" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H36" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="I36" t="s">
         <v>13</v>
@@ -1997,67 +1991,67 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>217</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>217</v>
       </c>
       <c r="D38" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E38" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="I38" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>110</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="D40" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E40" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F40" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="G40" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="I40" t="s">
         <v>13</v>
@@ -2065,33 +2059,33 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="D42" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E42" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F42" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="G42" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H42" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="I42" t="s">
         <v>13</v>
@@ -2099,33 +2093,33 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="D44" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E44" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F44" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H44" t="s">
-        <v>225</v>
+        <v>156</v>
       </c>
       <c r="I44" t="s">
         <v>13</v>
@@ -2133,33 +2127,33 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>42</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E46" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F46" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H46" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="I46" t="s">
         <v>13</v>
@@ -2167,41 +2161,41 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D48" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E48" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F48" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="I48" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2209,25 +2203,25 @@
         <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D50" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E50" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F50" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H50" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="I50" t="s">
         <v>13</v>
@@ -2235,7 +2229,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2243,25 +2237,25 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E52" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F52" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="G52" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H52" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="I52" t="s">
         <v>13</v>
@@ -2269,7 +2263,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2277,25 +2271,25 @@
         <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="C54" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="E54" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F54" t="s">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="G54" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="H54" t="s">
-        <v>236</v>
+        <v>15</v>
       </c>
       <c r="I54" t="s">
         <v>13</v>
@@ -2303,7 +2297,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2311,10 +2305,10 @@
         <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>237</v>
+        <v>39</v>
       </c>
       <c r="C56" t="s">
-        <v>237</v>
+        <v>39</v>
       </c>
       <c r="D56" t="s">
         <v>239</v>
@@ -2323,13 +2317,13 @@
         <v>240</v>
       </c>
       <c r="F56" t="s">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="G56" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>242</v>
+        <v>160</v>
       </c>
       <c r="I56" t="s">
         <v>13</v>
@@ -2337,7 +2331,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>238</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2345,25 +2339,25 @@
         <v>28</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D58" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E58" t="s">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="F58" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="G58" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H58" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="I58" t="s">
         <v>13</v>
@@ -2371,7 +2365,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2379,25 +2373,25 @@
         <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="C60" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="D60" t="s">
+        <v>243</v>
+      </c>
+      <c r="E60" t="s">
         <v>244</v>
       </c>
-      <c r="E60" t="s">
-        <v>245</v>
-      </c>
       <c r="F60" t="s">
-        <v>98</v>
+        <v>163</v>
       </c>
       <c r="G60" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H60" t="s">
-        <v>99</v>
+        <v>164</v>
       </c>
       <c r="I60" t="s">
         <v>13</v>
@@ -2405,7 +2399,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>68</v>
+        <v>162</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2413,25 +2407,25 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" t="s">
+        <v>245</v>
+      </c>
+      <c r="E62" t="s">
         <v>246</v>
       </c>
-      <c r="C62" t="s">
-        <v>246</v>
-      </c>
-      <c r="D62" t="s">
-        <v>248</v>
-      </c>
-      <c r="E62" t="s">
-        <v>249</v>
-      </c>
       <c r="F62" t="s">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="G62" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H62" t="s">
-        <v>251</v>
+        <v>102</v>
       </c>
       <c r="I62" t="s">
         <v>13</v>
@@ -2439,7 +2433,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>247</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2447,25 +2441,25 @@
         <v>31</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C64" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D64" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E64" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F64" t="s">
-        <v>254</v>
+        <v>73</v>
       </c>
       <c r="G64" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H64" t="s">
-        <v>211</v>
+        <v>46</v>
       </c>
       <c r="I64" t="s">
         <v>13</v>
@@ -2473,7 +2467,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2481,25 +2475,25 @@
         <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="D66" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E66" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F66" t="s">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="H66" t="s">
-        <v>258</v>
+        <v>75</v>
       </c>
       <c r="I66" t="s">
         <v>13</v>
@@ -2507,7 +2501,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2515,25 +2509,25 @@
         <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="D68" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E68" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F68" t="s">
-        <v>261</v>
+        <v>31</v>
       </c>
       <c r="G68" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H68" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I68" t="s">
         <v>13</v>
@@ -2541,7 +2535,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -2549,25 +2543,25 @@
         <v>34</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="C70" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="D70" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="E70" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="F70" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="G70" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H70" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="I70" t="s">
         <v>13</v>
@@ -2575,7 +2569,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>120</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -2583,25 +2577,25 @@
         <v>35</v>
       </c>
       <c r="B72" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C72" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D72" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E72" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F72" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G72" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H72" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="I72" t="s">
         <v>13</v>
@@ -2609,7 +2603,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -2617,25 +2611,25 @@
         <v>36</v>
       </c>
       <c r="B74" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" t="s">
+        <v>22</v>
+      </c>
+      <c r="D74" t="s">
+        <v>257</v>
+      </c>
+      <c r="E74" t="s">
+        <v>258</v>
+      </c>
+      <c r="F74" t="s">
         <v>24</v>
-      </c>
-      <c r="C74" t="s">
-        <v>24</v>
-      </c>
-      <c r="D74" t="s">
-        <v>266</v>
-      </c>
-      <c r="E74" t="s">
-        <v>267</v>
-      </c>
-      <c r="F74" t="s">
-        <v>26</v>
       </c>
       <c r="G74" t="s">
         <v>12</v>
       </c>
       <c r="H74" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I74" t="s">
         <v>13</v>
@@ -2643,7 +2637,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -2651,25 +2645,25 @@
         <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>268</v>
+        <v>55</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>55</v>
       </c>
       <c r="D76" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E76" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="F76" t="s">
-        <v>272</v>
+        <v>57</v>
       </c>
       <c r="G76" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H76" t="s">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="I76" t="s">
         <v>13</v>
@@ -2677,7 +2671,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>269</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -2685,25 +2679,25 @@
         <v>38</v>
       </c>
       <c r="B78" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="D78" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="E78" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="F78" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="G78" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H78" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I78" t="s">
         <v>13</v>
@@ -2711,7 +2705,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -2719,25 +2713,25 @@
         <v>39</v>
       </c>
       <c r="B80" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C80" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D80" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E80" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="F80" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G80" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H80" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I80" t="s">
         <v>13</v>
@@ -2745,7 +2739,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -2753,25 +2747,25 @@
         <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C82" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D82" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="E82" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="F82" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="G82" t="s">
         <v>12</v>
       </c>
       <c r="H82" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="I82" t="s">
         <v>13</v>
@@ -2779,7 +2773,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -2787,25 +2781,25 @@
         <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>279</v>
+        <v>60</v>
       </c>
       <c r="C84" t="s">
-        <v>279</v>
+        <v>60</v>
       </c>
       <c r="D84" t="s">
-        <v>281</v>
+        <v>182</v>
       </c>
       <c r="E84" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="F84" t="s">
-        <v>283</v>
+        <v>62</v>
       </c>
       <c r="G84" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H84" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="I84" t="s">
         <v>13</v>
@@ -2813,7 +2807,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>280</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -2821,25 +2815,25 @@
         <v>42</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="C86" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="D86" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E86" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="F86" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="G86" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H86" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I86" t="s">
         <v>13</v>
@@ -2847,7 +2841,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>79</v>
+        <v>180</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -2855,25 +2849,25 @@
         <v>43</v>
       </c>
       <c r="B88" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C88" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="D88" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="E88" t="s">
-        <v>289</v>
+        <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="G88" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H88" t="s">
-        <v>49</v>
+        <v>274</v>
       </c>
       <c r="I88" t="s">
         <v>13</v>
@@ -2881,7 +2875,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -2889,33 +2883,33 @@
         <v>44</v>
       </c>
       <c r="B90" t="s">
-        <v>63</v>
+        <v>275</v>
       </c>
       <c r="C90" t="s">
-        <v>63</v>
+        <v>275</v>
       </c>
       <c r="D90" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="E90" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="F90" t="s">
-        <v>65</v>
+        <v>279</v>
       </c>
       <c r="G90" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H90" t="s">
-        <v>17</v>
+        <v>280</v>
       </c>
       <c r="I90" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>64</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -2923,33 +2917,33 @@
         <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>69</v>
+        <v>281</v>
       </c>
       <c r="C92" t="s">
-        <v>69</v>
+        <v>281</v>
       </c>
       <c r="D92" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="E92" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F92" t="s">
-        <v>76</v>
+        <v>285</v>
       </c>
       <c r="G92" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H92" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="I92" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>70</v>
+        <v>282</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -2957,25 +2951,25 @@
         <v>46</v>
       </c>
       <c r="B94" t="s">
-        <v>128</v>
+        <v>286</v>
       </c>
       <c r="C94" t="s">
-        <v>128</v>
+        <v>286</v>
       </c>
       <c r="D94" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E94" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="F94" t="s">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="G94" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="I94" t="s">
         <v>13</v>
@@ -2983,7 +2977,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>129</v>
+        <v>287</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -2991,33 +2985,33 @@
         <v>47</v>
       </c>
       <c r="B96" t="s">
-        <v>132</v>
+        <v>291</v>
       </c>
       <c r="C96" t="s">
-        <v>132</v>
+        <v>291</v>
       </c>
       <c r="D96" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E96" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F96" t="s">
-        <v>134</v>
+        <v>295</v>
       </c>
       <c r="G96" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H96" t="s">
-        <v>135</v>
+        <v>296</v>
       </c>
       <c r="I96" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>133</v>
+        <v>292</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -3025,25 +3019,25 @@
         <v>48</v>
       </c>
       <c r="B98" t="s">
+        <v>297</v>
+      </c>
+      <c r="C98" t="s">
+        <v>297</v>
+      </c>
+      <c r="D98" t="s">
         <v>299</v>
       </c>
-      <c r="C98" t="s">
-        <v>299</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>300</v>
+      </c>
+      <c r="F98" t="s">
         <v>301</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
+        <v>10</v>
+      </c>
+      <c r="H98" t="s">
         <v>302</v>
-      </c>
-      <c r="F98" t="s">
-        <v>303</v>
-      </c>
-      <c r="G98" t="s">
-        <v>28</v>
-      </c>
-      <c r="H98" t="s">
-        <v>304</v>
       </c>
       <c r="I98" t="s">
         <v>11</v>
@@ -3051,7 +3045,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -3059,10 +3053,10 @@
         <v>49</v>
       </c>
       <c r="B100" t="s">
-        <v>14</v>
+        <v>303</v>
       </c>
       <c r="C100" t="s">
-        <v>14</v>
+        <v>303</v>
       </c>
       <c r="D100" t="s">
         <v>305</v>
@@ -3074,18 +3068,18 @@
         <v>307</v>
       </c>
       <c r="G100" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H100" t="s">
-        <v>43</v>
+        <v>308</v>
       </c>
       <c r="I100" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>15</v>
+        <v>304</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -3093,25 +3087,25 @@
         <v>50</v>
       </c>
       <c r="B102" t="s">
-        <v>308</v>
+        <v>176</v>
       </c>
       <c r="C102" t="s">
-        <v>308</v>
+        <v>176</v>
       </c>
       <c r="D102" t="s">
+        <v>309</v>
+      </c>
+      <c r="E102" t="s">
         <v>310</v>
       </c>
-      <c r="E102" t="s">
-        <v>136</v>
-      </c>
       <c r="F102" t="s">
-        <v>311</v>
+        <v>178</v>
       </c>
       <c r="G102" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H102" t="s">
-        <v>312</v>
+        <v>107</v>
       </c>
       <c r="I102" t="s">
         <v>13</v>
@@ -3119,7 +3113,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>309</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
+++ b/14_stocks_analysis/01_rankings_sector/2604_health.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebc00a0f969ad489/Programmazione/github/FromZeroToQuant-/14_stocks_analysis/01_rankings_sector/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57867E9F-4360-4EB5-9095-EBD2BE8AC3B2}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{CDCAC623-BF53-4FC5-BEC5-E003D9CDBCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34DA0305-AD28-4E4D-BACE-E002278F2945}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5AC1432C-0454-491C-B311-8CBC9194BD16}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="306">
   <si>
     <t>Symbol</t>
   </si>
@@ -209,15 +209,9 @@
     <t>LONN.SW</t>
   </si>
   <si>
-    <t>3.88</t>
-  </si>
-  <si>
     <t>-2.56</t>
   </si>
   <si>
-    <t>3.66</t>
-  </si>
-  <si>
     <t>Healthcare Services Group, Inc.</t>
   </si>
   <si>
@@ -236,15 +230,6 @@
     <t>CNC</t>
   </si>
   <si>
-    <t>Medpace Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>MEDP</t>
-  </si>
-  <si>
-    <t>7.14</t>
-  </si>
-  <si>
     <t>Option Care Health, Inc.</t>
   </si>
   <si>
@@ -266,18 +251,6 @@
     <t>-3.29</t>
   </si>
   <si>
-    <t>Molina Healthcare, Inc.</t>
-  </si>
-  <si>
-    <t>MOH</t>
-  </si>
-  <si>
-    <t>3.85</t>
-  </si>
-  <si>
-    <t>-4.20</t>
-  </si>
-  <si>
     <t>NeoGenomics, Inc.</t>
   </si>
   <si>
@@ -326,18 +299,6 @@
     <t>HSTM</t>
   </si>
   <si>
-    <t>EssilorLuxottica S.A.</t>
-  </si>
-  <si>
-    <t>EL.PA</t>
-  </si>
-  <si>
-    <t>-2.68</t>
-  </si>
-  <si>
-    <t>Steady</t>
-  </si>
-  <si>
     <t>-3.51</t>
   </si>
   <si>
@@ -428,30 +389,12 @@
     <t>2.48</t>
   </si>
   <si>
-    <t>3.44B</t>
-  </si>
-  <si>
     <t>Fresenius Medical Care AG &amp; Co. KGaA</t>
   </si>
   <si>
     <t>FME.DE</t>
   </si>
   <si>
-    <t>1.31</t>
-  </si>
-  <si>
-    <t>-2.43</t>
-  </si>
-  <si>
-    <t>Grifols, S.A.</t>
-  </si>
-  <si>
-    <t>GRF.MC</t>
-  </si>
-  <si>
-    <t>1.06</t>
-  </si>
-  <si>
     <t>-2.39</t>
   </si>
   <si>
@@ -464,27 +407,6 @@
     <t>3.22</t>
   </si>
   <si>
-    <t>Kyowa Kirin Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4151.T</t>
-  </si>
-  <si>
-    <t>6.34</t>
-  </si>
-  <si>
-    <t>-3.02</t>
-  </si>
-  <si>
-    <t>Haemonetics Corporation</t>
-  </si>
-  <si>
-    <t>HAE</t>
-  </si>
-  <si>
-    <t>2.08</t>
-  </si>
-  <si>
     <t>Recordati Industria Chimica e Farmaceutica S.p.A.</t>
   </si>
   <si>
@@ -521,18 +443,6 @@
     <t>-3.55</t>
   </si>
   <si>
-    <t>Daiichi Sankyo Company, Limited</t>
-  </si>
-  <si>
-    <t>4568.T</t>
-  </si>
-  <si>
-    <t>2.93</t>
-  </si>
-  <si>
-    <t>-2.08</t>
-  </si>
-  <si>
     <t>Theravance Biopharma, Inc.</t>
   </si>
   <si>
@@ -572,9 +482,6 @@
     <t>IDXX</t>
   </si>
   <si>
-    <t>2.74</t>
-  </si>
-  <si>
     <t>Electromed, Inc.</t>
   </si>
   <si>
@@ -584,297 +491,27 @@
     <t>14.47</t>
   </si>
   <si>
-    <t>1.48B</t>
-  </si>
-  <si>
-    <t>7.15B</t>
-  </si>
-  <si>
-    <t>+115.75</t>
-  </si>
-  <si>
-    <t>43.40M</t>
-  </si>
-  <si>
-    <t>+267.74</t>
-  </si>
-  <si>
-    <t>1.62B</t>
-  </si>
-  <si>
-    <t>+141.96</t>
-  </si>
-  <si>
-    <t>458.83M</t>
-  </si>
-  <si>
-    <t>+79.80</t>
-  </si>
-  <si>
-    <t>2.23B</t>
-  </si>
-  <si>
-    <t>+69.22</t>
-  </si>
-  <si>
-    <t>234.47M</t>
-  </si>
-  <si>
-    <t>+51.01</t>
-  </si>
-  <si>
-    <t>2.00B</t>
-  </si>
-  <si>
-    <t>+48.18</t>
-  </si>
-  <si>
-    <t>3.25B</t>
-  </si>
-  <si>
-    <t>+65.06</t>
-  </si>
-  <si>
-    <t>+61.25</t>
-  </si>
-  <si>
-    <t>6.06B</t>
-  </si>
-  <si>
-    <t>+61.03</t>
-  </si>
-  <si>
-    <t>8.14B</t>
-  </si>
-  <si>
-    <t>+58.90</t>
-  </si>
-  <si>
-    <t>9.34B</t>
-  </si>
-  <si>
-    <t>+37.08</t>
-  </si>
-  <si>
-    <t>+22.26</t>
-  </si>
-  <si>
-    <t>12.25B</t>
-  </si>
-  <si>
-    <t>+52.40</t>
-  </si>
-  <si>
-    <t>835.19M</t>
-  </si>
-  <si>
-    <t>+12.79</t>
-  </si>
-  <si>
-    <t>793.59M</t>
-  </si>
-  <si>
-    <t>+90.01</t>
-  </si>
-  <si>
-    <t>7.22B</t>
-  </si>
-  <si>
-    <t>+104.27</t>
-  </si>
-  <si>
-    <t>1.40B</t>
-  </si>
-  <si>
-    <t>+71.86</t>
-  </si>
-  <si>
     <t>WuXi Biologics (Cayman) Inc.</t>
   </si>
   <si>
     <t>2269.HK</t>
   </si>
   <si>
-    <t>16.97B</t>
-  </si>
-  <si>
-    <t>+31.76</t>
-  </si>
-  <si>
     <t>8.13</t>
   </si>
   <si>
     <t>-2.31</t>
   </si>
   <si>
-    <t>7.85B</t>
-  </si>
-  <si>
-    <t>+31.54</t>
-  </si>
-  <si>
-    <t>12.07B</t>
-  </si>
-  <si>
-    <t>+26.20</t>
-  </si>
-  <si>
-    <t>676.23M</t>
-  </si>
-  <si>
-    <t>+15.25</t>
-  </si>
-  <si>
-    <t>163.61B</t>
-  </si>
-  <si>
-    <t>+123.79</t>
-  </si>
-  <si>
-    <t>93.76B</t>
-  </si>
-  <si>
-    <t>+20.45</t>
-  </si>
-  <si>
-    <t>26.13B</t>
-  </si>
-  <si>
-    <t>+113.15</t>
-  </si>
-  <si>
-    <t>32.94B</t>
-  </si>
-  <si>
-    <t>+110.94</t>
-  </si>
-  <si>
-    <t>2.72B</t>
-  </si>
-  <si>
-    <t>+26.00</t>
-  </si>
-  <si>
-    <t>12.80B</t>
-  </si>
-  <si>
-    <t>+24.14</t>
-  </si>
-  <si>
     <t>11.94B</t>
   </si>
   <si>
-    <t>+21.32</t>
-  </si>
-  <si>
-    <t>30.71B</t>
-  </si>
-  <si>
-    <t>+55.94</t>
-  </si>
-  <si>
-    <t>41.10B</t>
-  </si>
-  <si>
-    <t>+24.74</t>
-  </si>
-  <si>
-    <t>66.19B</t>
-  </si>
-  <si>
-    <t>+19.23</t>
-  </si>
-  <si>
-    <t>10.56B</t>
-  </si>
-  <si>
-    <t>+17.19</t>
-  </si>
-  <si>
-    <t>13.44B</t>
-  </si>
-  <si>
-    <t>+14.76</t>
-  </si>
-  <si>
-    <t>11.06B</t>
-  </si>
-  <si>
-    <t>+38.44</t>
-  </si>
-  <si>
-    <t>29.08B</t>
-  </si>
-  <si>
-    <t>+17.18</t>
-  </si>
-  <si>
-    <t>148.67M</t>
-  </si>
-  <si>
-    <t>+14.53</t>
-  </si>
-  <si>
-    <t>43.42B</t>
-  </si>
-  <si>
-    <t>+13.22</t>
-  </si>
-  <si>
-    <t>9.49B</t>
-  </si>
-  <si>
-    <t>+11.31</t>
-  </si>
-  <si>
-    <t>714.13M</t>
-  </si>
-  <si>
-    <t>+7.08</t>
-  </si>
-  <si>
-    <t>21.89B</t>
-  </si>
-  <si>
-    <t>+3.92</t>
-  </si>
-  <si>
-    <t>-3.92</t>
-  </si>
-  <si>
-    <t>314.98M</t>
-  </si>
-  <si>
-    <t>-8.86</t>
-  </si>
-  <si>
-    <t>Definitive Healthcare Corp.</t>
-  </si>
-  <si>
-    <t>DH</t>
-  </si>
-  <si>
-    <t>91.32M</t>
-  </si>
-  <si>
-    <t>-0.60</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
     <t>Middle East Pharmaceutical Industries Company</t>
   </si>
   <si>
     <t>4016.SR</t>
   </si>
   <si>
-    <t>303.34M</t>
-  </si>
-  <si>
-    <t>+165.19</t>
-  </si>
-  <si>
     <t>9.74</t>
   </si>
   <si>
@@ -887,12 +524,6 @@
     <t>GMED</t>
   </si>
   <si>
-    <t>10.78B</t>
-  </si>
-  <si>
-    <t>+89.94</t>
-  </si>
-  <si>
     <t>11.56</t>
   </si>
   <si>
@@ -902,12 +533,6 @@
     <t>MTD</t>
   </si>
   <si>
-    <t>21.61B</t>
-  </si>
-  <si>
-    <t>+38.68</t>
-  </si>
-  <si>
     <t>6.35</t>
   </si>
   <si>
@@ -917,12 +542,6 @@
     <t>NAGE</t>
   </si>
   <si>
-    <t>297.29M</t>
-  </si>
-  <si>
-    <t>+95.70</t>
-  </si>
-  <si>
     <t>6.99</t>
   </si>
   <si>
@@ -935,12 +554,6 @@
     <t>STE</t>
   </si>
   <si>
-    <t>21.03B</t>
-  </si>
-  <si>
-    <t>+84.15</t>
-  </si>
-  <si>
     <t>4.71</t>
   </si>
   <si>
@@ -953,22 +566,394 @@
     <t>DXCM</t>
   </si>
   <si>
-    <t>25.57B</t>
-  </si>
-  <si>
-    <t>+84.08</t>
-  </si>
-  <si>
     <t>6.12</t>
   </si>
   <si>
     <t>-2.92</t>
   </si>
   <si>
-    <t>43.97B</t>
-  </si>
-  <si>
-    <t>+6.22</t>
+    <t>54.35M</t>
+  </si>
+  <si>
+    <t>+193.63</t>
+  </si>
+  <si>
+    <t>1.59B</t>
+  </si>
+  <si>
+    <t>+146.55</t>
+  </si>
+  <si>
+    <t>166.96B</t>
+  </si>
+  <si>
+    <t>+119.30</t>
+  </si>
+  <si>
+    <t>25.67B</t>
+  </si>
+  <si>
+    <t>+116.33</t>
+  </si>
+  <si>
+    <t>7.64B</t>
+  </si>
+  <si>
+    <t>+103.00</t>
+  </si>
+  <si>
+    <t>Genmab A/S</t>
+  </si>
+  <si>
+    <t>GMAB.CO</t>
+  </si>
+  <si>
+    <t>16.28B</t>
+  </si>
+  <si>
+    <t>+58.62</t>
+  </si>
+  <si>
+    <t>12.71</t>
+  </si>
+  <si>
+    <t>-2.63</t>
+  </si>
+  <si>
+    <t>539.27M</t>
+  </si>
+  <si>
+    <t>+52.98</t>
+  </si>
+  <si>
+    <t>236.93M</t>
+  </si>
+  <si>
+    <t>+49.20</t>
+  </si>
+  <si>
+    <t>9.32B</t>
+  </si>
+  <si>
+    <t>+37.41</t>
+  </si>
+  <si>
+    <t>40.58B</t>
+  </si>
+  <si>
+    <t>+26.82</t>
+  </si>
+  <si>
+    <t>+22.91</t>
+  </si>
+  <si>
+    <t>44.88B</t>
+  </si>
+  <si>
+    <t>+16.79</t>
+  </si>
+  <si>
+    <t>20.26</t>
+  </si>
+  <si>
+    <t>32.79B</t>
+  </si>
+  <si>
+    <t>+111.89</t>
+  </si>
+  <si>
+    <t>+73.00</t>
+  </si>
+  <si>
+    <t>1.79</t>
+  </si>
+  <si>
+    <t>823.54M</t>
+  </si>
+  <si>
+    <t>+14.38</t>
+  </si>
+  <si>
+    <t>1.30B</t>
+  </si>
+  <si>
+    <t>+83.97</t>
+  </si>
+  <si>
+    <t>854.32M</t>
+  </si>
+  <si>
+    <t>+76.50</t>
+  </si>
+  <si>
+    <t>Tenet Healthcare Corporation</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>15.22B</t>
+  </si>
+  <si>
+    <t>+36.42</t>
+  </si>
+  <si>
+    <t>1.85</t>
+  </si>
+  <si>
+    <t>-2.46</t>
+  </si>
+  <si>
+    <t>9.29B</t>
+  </si>
+  <si>
+    <t>+33.26</t>
+  </si>
+  <si>
+    <t>17.13B</t>
+  </si>
+  <si>
+    <t>+30.41</t>
+  </si>
+  <si>
+    <t>12.26B</t>
+  </si>
+  <si>
+    <t>+24.85</t>
+  </si>
+  <si>
+    <t>13.04B</t>
+  </si>
+  <si>
+    <t>+21.85</t>
+  </si>
+  <si>
+    <t>29.33B</t>
+  </si>
+  <si>
+    <t>+16.17</t>
+  </si>
+  <si>
+    <t>141.50M</t>
+  </si>
+  <si>
+    <t>+20.34</t>
+  </si>
+  <si>
+    <t>746.75M</t>
+  </si>
+  <si>
+    <t>+4.37</t>
+  </si>
+  <si>
+    <t>733.52M</t>
+  </si>
+  <si>
+    <t>+4.25</t>
+  </si>
+  <si>
+    <t>1.44B</t>
+  </si>
+  <si>
+    <t>-0.97</t>
+  </si>
+  <si>
+    <t>309.73M</t>
+  </si>
+  <si>
+    <t>-7.32</t>
+  </si>
+  <si>
+    <t>23.24B</t>
+  </si>
+  <si>
+    <t>315.14M</t>
+  </si>
+  <si>
+    <t>+154.85</t>
+  </si>
+  <si>
+    <t>308.48M</t>
+  </si>
+  <si>
+    <t>+88.60</t>
+  </si>
+  <si>
+    <t>28.40B</t>
+  </si>
+  <si>
+    <t>+65.73</t>
+  </si>
+  <si>
+    <t>IQVIA Holdings Inc.</t>
+  </si>
+  <si>
+    <t>IQV</t>
+  </si>
+  <si>
+    <t>30.68B</t>
+  </si>
+  <si>
+    <t>+25.66</t>
+  </si>
+  <si>
+    <t>1.83</t>
+  </si>
+  <si>
+    <t>-2.87</t>
+  </si>
+  <si>
+    <t>23.95B</t>
+  </si>
+  <si>
+    <t>+25.13</t>
+  </si>
+  <si>
+    <t>63.94B</t>
+  </si>
+  <si>
+    <t>+23.44</t>
+  </si>
+  <si>
+    <t>12.95B</t>
+  </si>
+  <si>
+    <t>+19.51</t>
+  </si>
+  <si>
+    <t>Sonova Holding AG</t>
+  </si>
+  <si>
+    <t>SOON.SW</t>
+  </si>
+  <si>
+    <t>16.09B</t>
+  </si>
+  <si>
+    <t>-5.59</t>
+  </si>
+  <si>
+    <t>4.81</t>
+  </si>
+  <si>
+    <t>-3.49</t>
+  </si>
+  <si>
+    <t>12.50B</t>
+  </si>
+  <si>
+    <t>+22.53</t>
+  </si>
+  <si>
+    <t>44.95B</t>
+  </si>
+  <si>
+    <t>+10.41</t>
+  </si>
+  <si>
+    <t>3.90</t>
+  </si>
+  <si>
+    <t>20.89B</t>
+  </si>
+  <si>
+    <t>+85.40</t>
+  </si>
+  <si>
+    <t>Boston Scientific Corporation</t>
+  </si>
+  <si>
+    <t>BSX</t>
+  </si>
+  <si>
+    <t>71.74B</t>
+  </si>
+  <si>
+    <t>+116.85</t>
+  </si>
+  <si>
+    <t>4.17</t>
+  </si>
+  <si>
+    <t>-2.20</t>
+  </si>
+  <si>
+    <t>11.08B</t>
+  </si>
+  <si>
+    <t>+84.72</t>
+  </si>
+  <si>
+    <t>OptimizeRx Corporation</t>
+  </si>
+  <si>
+    <t>OPRX</t>
+  </si>
+  <si>
+    <t>97.37M</t>
+  </si>
+  <si>
+    <t>+81.50</t>
+  </si>
+  <si>
+    <t>2.46</t>
+  </si>
+  <si>
+    <t>-2.52</t>
+  </si>
+  <si>
+    <t>Sanofi</t>
+  </si>
+  <si>
+    <t>SAN.PA</t>
+  </si>
+  <si>
+    <t>105.73B</t>
+  </si>
+  <si>
+    <t>+74.03</t>
+  </si>
+  <si>
+    <t>1.93</t>
+  </si>
+  <si>
+    <t>-1.64</t>
+  </si>
+  <si>
+    <t>7.86B</t>
+  </si>
+  <si>
+    <t>+64.53</t>
+  </si>
+  <si>
+    <t>3.27B</t>
+  </si>
+  <si>
+    <t>+64.11</t>
+  </si>
+  <si>
+    <t>2.30B</t>
+  </si>
+  <si>
+    <t>+64.02</t>
+  </si>
+  <si>
+    <t>6.05B</t>
+  </si>
+  <si>
+    <t>+60.75</t>
+  </si>
+  <si>
+    <t>3.50B</t>
+  </si>
+  <si>
+    <t>+58.20</t>
+  </si>
+  <si>
+    <t>2.07B</t>
+  </si>
+  <si>
+    <t>+42.96</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8295A055-0859-4227-AD35-9F88769F91FB}">
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -1387,25 +1372,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F2" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -1413,7 +1398,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1421,25 +1406,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
@@ -1447,7 +1432,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1455,25 +1440,25 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F6" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="I6" t="s">
         <v>13</v>
@@ -1481,7 +1466,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1489,25 +1474,25 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E8" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F8" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="I8" t="s">
         <v>13</v>
@@ -1515,7 +1500,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1523,25 +1508,25 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="I10" t="s">
         <v>13</v>
@@ -1549,7 +1534,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1557,25 +1542,25 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="D12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
         <v>193</v>
-      </c>
-      <c r="E12" t="s">
-        <v>194</v>
-      </c>
-      <c r="F12" t="s">
-        <v>141</v>
-      </c>
-      <c r="G12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" t="s">
-        <v>51</v>
       </c>
       <c r="I12" t="s">
         <v>13</v>
@@ -1583,7 +1568,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1591,25 +1576,25 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>194</v>
+      </c>
+      <c r="E14" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" t="s">
         <v>113</v>
-      </c>
-      <c r="C14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" t="s">
-        <v>195</v>
-      </c>
-      <c r="E14" t="s">
-        <v>196</v>
-      </c>
-      <c r="F14" t="s">
-        <v>172</v>
-      </c>
-      <c r="G14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" t="s">
-        <v>138</v>
       </c>
       <c r="I14" t="s">
         <v>13</v>
@@ -1617,7 +1602,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1625,25 +1610,25 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" t="s">
         <v>197</v>
       </c>
-      <c r="E16" t="s">
-        <v>198</v>
-      </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="I16" t="s">
         <v>13</v>
@@ -1651,7 +1636,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1659,25 +1644,25 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="E18" t="s">
         <v>199</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H18" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I18" t="s">
         <v>13</v>
@@ -1685,7 +1670,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1693,10 +1678,10 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
         <v>200</v>
@@ -1705,13 +1690,13 @@
         <v>201</v>
       </c>
       <c r="F20" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H20" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s">
         <v>13</v>
@@ -1719,7 +1704,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1727,25 +1712,25 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" t="s">
         <v>202</v>
       </c>
-      <c r="E22" t="s">
-        <v>203</v>
-      </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H22" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I22" t="s">
         <v>13</v>
@@ -1753,7 +1738,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1761,25 +1746,25 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="D24" t="s">
+        <v>203</v>
+      </c>
+      <c r="E24" t="s">
         <v>204</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>205</v>
       </c>
-      <c r="F24" t="s">
-        <v>121</v>
-      </c>
       <c r="G24" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H24" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="I24" t="s">
         <v>13</v>
@@ -1787,7 +1772,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1795,25 +1780,25 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>206</v>
       </c>
       <c r="E26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F26" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H26" t="s">
-        <v>156</v>
+        <v>94</v>
       </c>
       <c r="I26" t="s">
         <v>13</v>
@@ -1821,7 +1806,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1829,25 +1814,25 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="E28" t="s">
         <v>208</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="G28" t="s">
         <v>26</v>
       </c>
       <c r="H28" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="I28" t="s">
         <v>13</v>
@@ -1855,7 +1840,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1863,25 +1848,25 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F30" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="G30" t="s">
         <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="I30" t="s">
         <v>13</v>
@@ -1889,7 +1874,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1897,25 +1882,25 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E32" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F32" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="G32" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H32" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="I32" t="s">
         <v>13</v>
@@ -1923,7 +1908,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1931,25 +1916,25 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E34" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F34" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I34" t="s">
         <v>13</v>
@@ -1957,7 +1942,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1965,25 +1950,25 @@
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="D36" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E36" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F36" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="G36" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="I36" t="s">
         <v>13</v>
@@ -1991,7 +1976,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1999,25 +1984,25 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>217</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>217</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E38" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F38" t="s">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H38" t="s">
-        <v>222</v>
+        <v>70</v>
       </c>
       <c r="I38" t="s">
         <v>13</v>
@@ -2025,7 +2010,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>218</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2033,25 +2018,25 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D40" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E40" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F40" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="G40" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H40" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I40" t="s">
         <v>13</v>
@@ -2059,7 +2044,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2067,25 +2052,25 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="D42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F42" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="G42" t="s">
         <v>26</v>
       </c>
       <c r="H42" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="I42" t="s">
         <v>13</v>
@@ -2093,7 +2078,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2101,25 +2086,25 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="D44" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E44" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F44" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="I44" t="s">
         <v>13</v>
@@ -2127,7 +2112,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>174</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2135,25 +2120,25 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E46" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F46" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H46" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="I46" t="s">
         <v>13</v>
@@ -2161,67 +2146,67 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="D48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F48" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="I48" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="D50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F50" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H50" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="I50" t="s">
         <v>13</v>
@@ -2229,33 +2214,33 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C52" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E52" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F52" t="s">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H52" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="I52" t="s">
         <v>13</v>
@@ -2263,27 +2248,27 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E54" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F54" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="G54" t="s">
         <v>21</v>
@@ -2297,33 +2282,33 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>147</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="C56" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="D56" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E56" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F56" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G56" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H56" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="I56" t="s">
         <v>13</v>
@@ -2331,33 +2316,33 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>40</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E58" t="s">
-        <v>242</v>
+        <v>126</v>
       </c>
       <c r="F58" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="G58" t="s">
         <v>12</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="I58" t="s">
         <v>13</v>
@@ -2365,18 +2350,18 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
@@ -2385,32 +2370,32 @@
         <v>244</v>
       </c>
       <c r="F60" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G60" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H60" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I60" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="D62" t="s">
         <v>245</v>
@@ -2419,32 +2404,32 @@
         <v>246</v>
       </c>
       <c r="F62" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="G62" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H62" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="I62" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>174</v>
       </c>
       <c r="C64" t="s">
-        <v>71</v>
+        <v>174</v>
       </c>
       <c r="D64" t="s">
         <v>247</v>
@@ -2453,47 +2438,47 @@
         <v>248</v>
       </c>
       <c r="F64" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H64" t="s">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="I64" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="C66" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="D66" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E66" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>253</v>
       </c>
       <c r="G66" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="I66" t="s">
         <v>13</v>
@@ -2501,33 +2486,33 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>36</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="D68" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E68" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F68" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c r="G68" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H68" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="I68" t="s">
         <v>13</v>
@@ -2535,33 +2520,33 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C70" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D70" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E70" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F70" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="G70" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H70" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="I70" t="s">
         <v>13</v>
@@ -2569,33 +2554,33 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C72" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="D72" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E72" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F72" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="G72" t="s">
         <v>21</v>
       </c>
       <c r="H72" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="I72" t="s">
         <v>13</v>
@@ -2603,33 +2588,33 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>261</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E74" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F74" t="s">
-        <v>24</v>
+        <v>265</v>
       </c>
       <c r="G74" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H74" t="s">
-        <v>25</v>
+        <v>266</v>
       </c>
       <c r="I74" t="s">
         <v>13</v>
@@ -2637,33 +2622,33 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>23</v>
+        <v>262</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C76" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D76" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E76" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F76" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G76" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H76" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I76" t="s">
         <v>13</v>
@@ -2671,33 +2656,33 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D78" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E78" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F78" t="s">
-        <v>78</v>
+        <v>271</v>
       </c>
       <c r="G78" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H78" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="I78" t="s">
         <v>13</v>
@@ -2705,169 +2690,169 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="D80" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="E80" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F80" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="G80" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H80" t="s">
-        <v>58</v>
+        <v>173</v>
       </c>
       <c r="I80" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>95</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="C82" t="s">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="D82" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E82" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="F82" t="s">
-        <v>110</v>
+        <v>278</v>
       </c>
       <c r="G82" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H82" t="s">
-        <v>111</v>
+        <v>279</v>
       </c>
       <c r="I82" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>109</v>
+        <v>275</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="C84" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="D84" t="s">
-        <v>182</v>
+        <v>280</v>
       </c>
       <c r="E84" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="F84" t="s">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="G84" t="s">
         <v>21</v>
       </c>
       <c r="H84" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="I84" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>282</v>
       </c>
       <c r="C86" t="s">
-        <v>179</v>
+        <v>282</v>
       </c>
       <c r="D86" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="E86" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="F86" t="s">
-        <v>181</v>
+        <v>286</v>
       </c>
       <c r="G86" t="s">
         <v>21</v>
       </c>
       <c r="H86" t="s">
-        <v>46</v>
+        <v>287</v>
       </c>
       <c r="I86" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>180</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="C88" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="D88" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="E88" t="s">
-        <v>112</v>
+        <v>291</v>
       </c>
       <c r="F88" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="G88" t="s">
         <v>21</v>
       </c>
       <c r="H88" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="I88" t="s">
         <v>13</v>
@@ -2875,101 +2860,101 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>275</v>
+        <v>33</v>
       </c>
       <c r="C90" t="s">
-        <v>275</v>
+        <v>33</v>
       </c>
       <c r="D90" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="E90" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="F90" t="s">
-        <v>279</v>
+        <v>18</v>
       </c>
       <c r="G90" t="s">
         <v>12</v>
       </c>
       <c r="H90" t="s">
-        <v>280</v>
+        <v>107</v>
       </c>
       <c r="I90" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>281</v>
+        <v>64</v>
       </c>
       <c r="C92" t="s">
-        <v>281</v>
+        <v>64</v>
       </c>
       <c r="D92" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="E92" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="F92" t="s">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="G92" t="s">
         <v>21</v>
       </c>
       <c r="H92" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="I92" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>282</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>286</v>
+        <v>114</v>
       </c>
       <c r="C94" t="s">
-        <v>286</v>
+        <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="E94" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="F94" t="s">
-        <v>290</v>
+        <v>116</v>
       </c>
       <c r="G94" t="s">
         <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="I94" t="s">
         <v>13</v>
@@ -2977,143 +2962,109 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>287</v>
+        <v>115</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>291</v>
+        <v>91</v>
       </c>
       <c r="C96" t="s">
-        <v>291</v>
+        <v>91</v>
       </c>
       <c r="D96" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="E96" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="F96" t="s">
-        <v>295</v>
+        <v>93</v>
       </c>
       <c r="G96" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H96" t="s">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="I96" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>292</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>297</v>
+        <v>52</v>
       </c>
       <c r="C98" t="s">
-        <v>297</v>
+        <v>52</v>
       </c>
       <c r="D98" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E98" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F98" t="s">
-        <v>301</v>
+        <v>54</v>
       </c>
       <c r="G98" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H98" t="s">
-        <v>302</v>
+        <v>87</v>
       </c>
       <c r="I98" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>298</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>303</v>
+        <v>100</v>
       </c>
       <c r="C100" t="s">
-        <v>303</v>
+        <v>100</v>
       </c>
       <c r="D100" t="s">
+        <v>304</v>
+      </c>
+      <c r="E100" t="s">
         <v>305</v>
       </c>
-      <c r="E100" t="s">
-        <v>306</v>
-      </c>
       <c r="F100" t="s">
-        <v>307</v>
+        <v>142</v>
       </c>
       <c r="G100" t="s">
         <v>26</v>
       </c>
       <c r="H100" t="s">
-        <v>308</v>
+        <v>119</v>
       </c>
       <c r="I100" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>50</v>
-      </c>
-      <c r="B102" t="s">
-        <v>176</v>
-      </c>
-      <c r="C102" t="s">
-        <v>176</v>
-      </c>
-      <c r="D102" t="s">
-        <v>309</v>
-      </c>
-      <c r="E102" t="s">
-        <v>310</v>
-      </c>
-      <c r="F102" t="s">
-        <v>178</v>
-      </c>
-      <c r="G102" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" t="s">
-        <v>107</v>
-      </c>
-      <c r="I102" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
-        <v>177</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
